--- a/SEOE/Update CG Calculation for Multiple Cases SBLC & RP 13th Aug.xlsx
+++ b/SEOE/Update CG Calculation for Multiple Cases SBLC & RP 13th Aug.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180" activeTab="4"/>
+    <workbookView windowWidth="24000" windowHeight="9600" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="New CG" sheetId="11" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="87">
   <si>
     <t>SBLC</t>
   </si>
@@ -299,6 +299,9 @@
   </si>
   <si>
     <t>Expiry date(To be added)</t>
+  </si>
+  <si>
+    <t>Fourth Update</t>
   </si>
 </sst>
 </file>
@@ -1057,7 +1060,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1127,6 +1130,9 @@
     </xf>
     <xf numFmtId="182" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1641,7 +1647,7 @@
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9" style="79"/>
+    <col min="1" max="1" width="9" style="80"/>
     <col min="2" max="2" width="11.8166666666667" style="4" customWidth="1"/>
     <col min="3" max="3" width="20" style="4" customWidth="1"/>
     <col min="4" max="4" width="15.1833333333333" style="4" customWidth="1"/>
@@ -1652,11 +1658,11 @@
     <col min="10" max="10" width="7.54166666666667" style="4" customWidth="1"/>
     <col min="11" max="11" width="8.90833333333333" style="4" customWidth="1"/>
     <col min="12" max="12" width="8.725" style="4" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="79"/>
+    <col min="13" max="16384" width="9" style="80"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5" spans="1:12">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="81" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
@@ -1693,7 +1699,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" s="78" customFormat="1" spans="1:12">
+    <row r="2" s="79" customFormat="1" spans="1:12">
       <c r="B2" s="16">
         <v>46147</v>
       </c>
@@ -1735,7 +1741,7 @@
       </c>
     </row>
     <row r="5" ht="42.75" spans="1:12">
-      <c r="A5" s="81" t="s">
+      <c r="A5" s="82" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="11" t="s">
@@ -1772,7 +1778,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" s="78" customFormat="1" spans="1:12">
+    <row r="6" s="79" customFormat="1" spans="1:12">
       <c r="B6" s="16">
         <v>46147</v>
       </c>
@@ -1825,73 +1831,73 @@
       </c>
     </row>
     <row r="15" ht="45" spans="1:12">
-      <c r="C15" s="82" t="s">
+      <c r="C15" s="83" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="82" t="s">
+      <c r="D15" s="83" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="82" t="s">
+      <c r="E15" s="83" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" ht="30" spans="1:12">
-      <c r="C16" s="82" t="s">
+      <c r="C16" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="82" t="s">
+      <c r="D16" s="83" t="s">
         <v>22</v>
       </c>
-      <c r="E16" s="82" t="s">
+      <c r="E16" s="83" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" ht="60" spans="3:5">
-      <c r="C17" s="82" t="s">
+      <c r="C17" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="D17" s="82" t="s">
+      <c r="D17" s="83" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="82" t="s">
+      <c r="E17" s="83" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" spans="3:5">
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
     </row>
     <row r="19" ht="45" spans="3:5">
-      <c r="C19" s="82" t="s">
+      <c r="C19" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="D19" s="82" t="s">
+      <c r="D19" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="82" t="s">
+      <c r="E19" s="83" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="20" ht="30" spans="3:5">
-      <c r="C20" s="82" t="s">
+      <c r="C20" s="83" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="82" t="s">
+      <c r="D20" s="83" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="82" t="s">
+      <c r="E20" s="83" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="21" spans="3:5">
-      <c r="C21" s="82" t="s">
+      <c r="C21" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="D21" s="82" t="s">
+      <c r="D21" s="83" t="s">
         <v>30</v>
       </c>
-      <c r="E21" s="82" t="s">
+      <c r="E21" s="83" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2093,14 +2099,14 @@
       </c>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="24">
+      <c r="A12" s="25">
         <v>2</v>
       </c>
-      <c r="B12" s="25"/>
-      <c r="C12" s="24" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="24" t="s">
+      <c r="D12" s="25" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2160,7 +2166,7 @@
       <c r="H14" s="17">
         <v>0.015</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="27">
         <f>C14*H14*D14/365</f>
         <v>9945.20547945206</v>
       </c>
@@ -2195,7 +2201,7 @@
       <c r="I15" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J15" s="27" t="s">
+      <c r="J15" s="28" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2211,7 +2217,7 @@
         <f>F16-E14+1</f>
         <v>242</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="29">
         <v>46204</v>
       </c>
       <c r="F16" s="16">
@@ -2223,15 +2229,15 @@
       <c r="H16" s="17">
         <v>0.015</v>
       </c>
-      <c r="I16" s="26">
+      <c r="I16" s="27">
         <f>C16*H16*D16/365</f>
         <v>14917.8082191781</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="27">
         <f>I16</f>
         <v>14917.8082191781</v>
       </c>
-      <c r="K16" s="76"/>
+      <c r="K16" s="77"/>
     </row>
     <row r="21" spans="1:10">
       <c r="B21" s="5"/>
@@ -2243,14 +2249,14 @@
       </c>
     </row>
     <row r="22" spans="1:10">
-      <c r="A22" s="29">
+      <c r="A22" s="30">
         <v>3</v>
       </c>
       <c r="B22" s="15"/>
-      <c r="C22" s="29" t="s">
+      <c r="C22" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="29" t="s">
+      <c r="D22" s="30" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2310,7 +2316,7 @@
       <c r="H24" s="17">
         <v>0.015</v>
       </c>
-      <c r="I24" s="26">
+      <c r="I24" s="27">
         <f>C24*H24*D24/365</f>
         <v>9945.20547945206</v>
       </c>
@@ -2377,7 +2383,7 @@
         <f>C26*H26*D26/365</f>
         <v>18678.0821917808</v>
       </c>
-      <c r="J26" s="26">
+      <c r="J26" s="27">
         <f>I26</f>
         <v>18678.0821917808</v>
       </c>
@@ -2395,14 +2401,14 @@
       </c>
     </row>
     <row r="33" spans="1:10">
-      <c r="A33" s="24">
+      <c r="A33" s="25">
         <v>4</v>
       </c>
-      <c r="B33" s="25"/>
-      <c r="C33" s="24" t="s">
+      <c r="B33" s="26"/>
+      <c r="C33" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="25" t="s">
         <v>54</v>
       </c>
     </row>
@@ -2462,7 +2468,7 @@
       <c r="H35" s="17">
         <v>0.015</v>
       </c>
-      <c r="I35" s="26">
+      <c r="I35" s="27">
         <f>C35*H35*D35/365</f>
         <v>9945.20547945206</v>
       </c>
@@ -2497,7 +2503,7 @@
       <c r="I36" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J36" s="27" t="s">
+      <c r="J36" s="28" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2529,13 +2535,13 @@
         <f>C37*H37*D37/365</f>
         <v>7438.35616438356</v>
       </c>
-      <c r="J37" s="30">
+      <c r="J37" s="31">
         <f>I37</f>
         <v>7438.35616438356</v>
       </c>
     </row>
     <row r="38" spans="1:10">
-      <c r="J38" s="31" t="s">
+      <c r="J38" s="32" t="s">
         <v>55</v>
       </c>
     </row>
@@ -2547,19 +2553,19 @@
       <c r="D43" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E43" s="77" t="s">
+      <c r="E43" s="78" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:10">
-      <c r="A44" s="24">
+      <c r="A44" s="25">
         <v>9</v>
       </c>
-      <c r="B44" s="25"/>
-      <c r="C44" s="24" t="s">
+      <c r="B44" s="26"/>
+      <c r="C44" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D44" s="24" t="s">
+      <c r="D44" s="25" t="s">
         <v>34</v>
       </c>
     </row>
@@ -2619,7 +2625,7 @@
       <c r="H46" s="17">
         <v>0.015</v>
       </c>
-      <c r="I46" s="26">
+      <c r="I46" s="27">
         <f>C46*H46*D46/365</f>
         <v>9945.20547945206</v>
       </c>
@@ -2654,7 +2660,7 @@
       <c r="I47" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J47" s="27" t="s">
+      <c r="J47" s="28" t="s">
         <v>46</v>
       </c>
     </row>
@@ -2687,7 +2693,7 @@
         <f>C48*H48*D48/365</f>
         <v>9945.20547945206</v>
       </c>
-      <c r="J48" s="30">
+      <c r="J48" s="31">
         <f>I48-I46</f>
         <v>0</v>
       </c>
@@ -2915,14 +2921,14 @@
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="24">
+      <c r="A11" s="25">
         <v>2</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="24" t="s">
+      <c r="B11" s="26"/>
+      <c r="C11" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="25" t="s">
         <v>34</v>
       </c>
     </row>
@@ -3014,7 +3020,7 @@
       <c r="I14" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K14" s="11" t="s">
@@ -3035,7 +3041,7 @@
       <c r="B15" s="13">
         <v>46267</v>
       </c>
-      <c r="C15" s="71">
+      <c r="C15" s="72">
         <v>1500000</v>
       </c>
       <c r="D15" s="20">
@@ -3087,14 +3093,14 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="29">
+      <c r="A20" s="30">
         <v>3</v>
       </c>
       <c r="B20" s="15"/>
-      <c r="C20" s="29" t="s">
+      <c r="C20" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D20" s="29" t="s">
+      <c r="D20" s="30" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3263,14 +3269,14 @@
       </c>
     </row>
     <row r="31" spans="1:14">
-      <c r="A31" s="24">
+      <c r="A31" s="25">
         <v>4</v>
       </c>
-      <c r="B31" s="25"/>
-      <c r="C31" s="24" t="s">
+      <c r="B31" s="26"/>
+      <c r="C31" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D31" s="24" t="s">
+      <c r="D31" s="25" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3439,14 +3445,14 @@
       </c>
     </row>
     <row r="41" spans="1:14">
-      <c r="A41" s="29">
+      <c r="A41" s="30">
         <v>5</v>
       </c>
       <c r="B41" s="15"/>
-      <c r="C41" s="29" t="s">
+      <c r="C41" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D41" s="29" t="s">
+      <c r="D41" s="30" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3542,7 +3548,7 @@
       <c r="I44" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J44" s="27" t="s">
+      <c r="J44" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K44" s="11" t="s">
@@ -3615,14 +3621,14 @@
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="29">
+      <c r="A52" s="30">
         <v>6</v>
       </c>
       <c r="B52" s="15"/>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D52" s="29" t="s">
+      <c r="D52" s="30" t="s">
         <v>35</v>
       </c>
     </row>
@@ -3791,14 +3797,14 @@
       </c>
     </row>
     <row r="64" spans="1:14">
-      <c r="A64" s="29">
+      <c r="A64" s="30">
         <v>7</v>
       </c>
       <c r="B64" s="15"/>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="D64" s="30" t="s">
         <v>54</v>
       </c>
     </row>
@@ -3968,14 +3974,14 @@
       </c>
     </row>
     <row r="75" spans="1:14">
-      <c r="A75" s="29">
+      <c r="A75" s="30">
         <v>8</v>
       </c>
       <c r="B75" s="15"/>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D75" s="29" t="s">
+      <c r="D75" s="30" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4071,7 +4077,7 @@
       <c r="I78" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J78" s="27" t="s">
+      <c r="J78" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K78" s="11" t="s">
@@ -4144,14 +4150,14 @@
       </c>
     </row>
     <row r="83" spans="1:14">
-      <c r="A83" s="29">
+      <c r="A83" s="30">
         <v>6</v>
       </c>
       <c r="B83" s="15"/>
-      <c r="C83" s="29" t="s">
+      <c r="C83" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D83" s="29" t="s">
+      <c r="D83" s="30" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4247,7 +4253,7 @@
       <c r="I86" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J86" s="27" t="s">
+      <c r="J86" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K86" s="11" t="s">
@@ -4275,7 +4281,7 @@
         <f>F87-E85+1</f>
         <v>611</v>
       </c>
-      <c r="E87" s="72"/>
+      <c r="E87" s="73"/>
       <c r="F87" s="21">
         <v>46634</v>
       </c>
@@ -4289,23 +4295,23 @@
         <f>M87+N87</f>
         <v>7865.75342465753</v>
       </c>
-      <c r="J87" s="30">
+      <c r="J87" s="31">
         <f>I87-I85</f>
         <v>1180.82191780822</v>
       </c>
-      <c r="K87" s="62">
+      <c r="K87" s="63">
         <f>B87-E85</f>
         <v>243</v>
       </c>
-      <c r="L87" s="62">
+      <c r="L87" s="63">
         <f>D87-K87</f>
         <v>368</v>
       </c>
-      <c r="M87" s="73">
+      <c r="M87" s="74">
         <f>C85*H85*K87/365</f>
         <v>3328.76712328767</v>
       </c>
-      <c r="N87" s="73">
+      <c r="N87" s="74">
         <f>C87*H87*L87/365</f>
         <v>4536.98630136986</v>
       </c>
@@ -4334,7 +4340,7 @@
       <c r="I88" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J88" s="27" t="s">
+      <c r="J88" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K88" s="11" t="s">
@@ -4421,7 +4427,7 @@
       <c r="I90" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J90" s="27" t="s">
+      <c r="J90" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K90" s="11" t="s">
@@ -4449,35 +4455,35 @@
         <f>F91-E85+1</f>
         <v>611</v>
       </c>
-      <c r="E91" s="72"/>
+      <c r="E91" s="73"/>
       <c r="F91" s="21">
         <v>46634</v>
       </c>
       <c r="G91" s="15"/>
-      <c r="H91" s="66">
+      <c r="H91" s="67">
         <v>0.005</v>
       </c>
-      <c r="I91" s="70">
+      <c r="I91" s="71">
         <f>M87+M89+M91+N91</f>
         <v>12900</v>
       </c>
-      <c r="J91" s="30">
+      <c r="J91" s="31">
         <f>I91-I85</f>
         <v>6215.06849315068</v>
       </c>
-      <c r="K91" s="62">
+      <c r="K91" s="63">
         <f>B91-E85</f>
         <v>362</v>
       </c>
-      <c r="L91" s="62">
+      <c r="L91" s="63">
         <f>D91-K91</f>
         <v>249</v>
       </c>
-      <c r="M91" s="74">
+      <c r="M91" s="75">
         <f>C89*K91*H91/365</f>
         <v>4463.01369863014</v>
       </c>
-      <c r="N91" s="74">
+      <c r="N91" s="75">
         <f>C91*H91*L91/365</f>
         <v>1705.47945205479</v>
       </c>
@@ -4490,19 +4496,19 @@
       <c r="D100" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E100" s="75" t="s">
+      <c r="E100" s="76" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="101" spans="1:14">
-      <c r="A101" s="24">
+      <c r="A101" s="25">
         <v>9</v>
       </c>
-      <c r="B101" s="25"/>
-      <c r="C101" s="24" t="s">
+      <c r="B101" s="26"/>
+      <c r="C101" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D101" s="24" t="s">
+      <c r="D101" s="25" t="s">
         <v>34</v>
       </c>
     </row>
@@ -4600,7 +4606,7 @@
       <c r="I104" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J104" s="27" t="s">
+      <c r="J104" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K104" s="11" t="s">
@@ -4714,7 +4720,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="59" t="s">
         <v>72</v>
       </c>
     </row>
@@ -4736,10 +4742,10 @@
     <row r="3" ht="30" spans="1:14">
       <c r="A3" s="15"/>
       <c r="B3" s="15"/>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="30" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="7" t="s">
@@ -4750,39 +4756,39 @@
       </c>
     </row>
     <row r="4" ht="42.75" spans="1:14">
-      <c r="A4" s="59" t="s">
+      <c r="A4" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="59" t="s">
+      <c r="C4" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="60" t="s">
         <v>62</v>
       </c>
-      <c r="G4" s="59" t="s">
+      <c r="G4" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="H4" s="59" t="s">
+      <c r="H4" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="I4" s="59" t="s">
+      <c r="I4" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="59" t="s">
+      <c r="J4" s="60" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="59"/>
+      <c r="A5" s="60"/>
       <c r="B5" s="13">
         <v>46024</v>
       </c>
@@ -4816,47 +4822,47 @@
       <c r="L5" s="15"/>
     </row>
     <row r="6" ht="42.75" spans="1:14">
-      <c r="A6" s="59" t="s">
+      <c r="A6" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E6" s="59"/>
-      <c r="F6" s="59" t="s">
+      <c r="E6" s="60"/>
+      <c r="F6" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="G6" s="59"/>
-      <c r="H6" s="59" t="s">
+      <c r="G6" s="60"/>
+      <c r="H6" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="59" t="s">
+      <c r="I6" s="60" t="s">
         <v>77</v>
       </c>
-      <c r="J6" s="59" t="s">
+      <c r="J6" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="K6" s="59" t="s">
+      <c r="K6" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="L6" s="59" t="s">
+      <c r="L6" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="M6" s="59" t="s">
+      <c r="M6" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="N6" s="59" t="s">
+      <c r="N6" s="60" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="59"/>
+      <c r="A7" s="60"/>
       <c r="B7" s="13">
         <v>46267</v>
       </c>
@@ -4877,73 +4883,73 @@
       <c r="H7" s="17">
         <v>0.005</v>
       </c>
-      <c r="I7" s="60">
+      <c r="I7" s="61">
         <f>M7+N7</f>
         <v>7865.75342465753</v>
       </c>
-      <c r="J7" s="61">
+      <c r="J7" s="62">
         <f>I7</f>
         <v>7865.75342465753</v>
       </c>
-      <c r="K7" s="62">
+      <c r="K7" s="63">
         <f>B7-E5</f>
         <v>243</v>
       </c>
-      <c r="L7" s="62">
+      <c r="L7" s="63">
         <f t="shared" ref="L7:L11" si="0">D7-K7</f>
         <v>368</v>
       </c>
-      <c r="M7" s="63">
+      <c r="M7" s="64">
         <f>C5*H5*K7/365</f>
         <v>3328.76712328767</v>
       </c>
-      <c r="N7" s="64">
+      <c r="N7" s="65">
         <f t="shared" ref="N7:N11" si="1">C7*H7*L7/365</f>
         <v>4536.98630136986</v>
       </c>
     </row>
     <row r="8" ht="31" customHeight="1" spans="1:14">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="59"/>
-      <c r="F8" s="59" t="s">
+      <c r="E8" s="60"/>
+      <c r="F8" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="G8" s="59"/>
-      <c r="H8" s="59" t="s">
+      <c r="G8" s="60"/>
+      <c r="H8" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="59" t="s">
+      <c r="I8" s="60" t="s">
         <v>78</v>
       </c>
-      <c r="J8" s="59" t="s">
+      <c r="J8" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="K8" s="59" t="s">
+      <c r="K8" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="L8" s="59" t="s">
+      <c r="L8" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="M8" s="59" t="s">
+      <c r="M8" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="N8" s="59" t="s">
+      <c r="N8" s="60" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1" spans="1:14">
-      <c r="A9" s="59"/>
+      <c r="A9" s="60"/>
       <c r="B9" s="13">
         <v>46300</v>
       </c>
@@ -4964,7 +4970,7 @@
       <c r="H9" s="17">
         <v>0.005</v>
       </c>
-      <c r="I9" s="60">
+      <c r="I9" s="61">
         <f>M9+N9</f>
         <v>7902.7397260274</v>
       </c>
@@ -4972,65 +4978,65 @@
         <f>I9+M7</f>
         <v>11231.5068493151</v>
       </c>
-      <c r="K9" s="65">
+      <c r="K9" s="66">
         <f>B9-E5</f>
         <v>276</v>
       </c>
-      <c r="L9" s="65">
+      <c r="L9" s="66">
         <f t="shared" si="0"/>
         <v>365</v>
       </c>
-      <c r="M9" s="64">
+      <c r="M9" s="65">
         <f>C7*H9*K9/365</f>
         <v>3402.7397260274</v>
       </c>
-      <c r="N9" s="64">
+      <c r="N9" s="65">
         <f t="shared" si="1"/>
         <v>4500</v>
       </c>
     </row>
     <row r="10" ht="42.75" spans="1:14">
-      <c r="A10" s="59" t="s">
+      <c r="A10" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E10" s="59"/>
-      <c r="F10" s="59" t="s">
+      <c r="E10" s="60"/>
+      <c r="F10" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="59"/>
-      <c r="H10" s="59" t="s">
+      <c r="G10" s="60"/>
+      <c r="H10" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="59" t="s">
+      <c r="I10" s="60" t="s">
         <v>79</v>
       </c>
-      <c r="J10" s="59" t="s">
+      <c r="J10" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="K10" s="59" t="s">
+      <c r="K10" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="L10" s="59" t="s">
+      <c r="L10" s="60" t="s">
         <v>66</v>
       </c>
-      <c r="M10" s="59" t="s">
+      <c r="M10" s="60" t="s">
         <v>67</v>
       </c>
-      <c r="N10" s="59" t="s">
+      <c r="N10" s="60" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="59"/>
+      <c r="A11" s="60"/>
       <c r="B11" s="13">
         <v>46386</v>
       </c>
@@ -5048,42 +5054,42 @@
       <c r="G11" s="15">
         <v>100</v>
       </c>
-      <c r="H11" s="66">
+      <c r="H11" s="67">
         <v>0.005</v>
       </c>
-      <c r="I11" s="67">
+      <c r="I11" s="68">
         <f>M11+N11</f>
         <v>6373.97260273973</v>
       </c>
-      <c r="J11" s="61">
+      <c r="J11" s="62">
         <f>I11+M9+M7</f>
         <v>13105.4794520548</v>
       </c>
-      <c r="K11" s="62">
+      <c r="K11" s="63">
         <f>B11-E5</f>
         <v>362</v>
       </c>
-      <c r="L11" s="62">
+      <c r="L11" s="63">
         <f t="shared" si="0"/>
         <v>279</v>
       </c>
-      <c r="M11" s="67">
+      <c r="M11" s="68">
         <f>C9*K11*H11/365</f>
         <v>4463.01369863014</v>
       </c>
-      <c r="N11" s="67">
+      <c r="N11" s="68">
         <f t="shared" si="1"/>
         <v>1910.95890410959</v>
       </c>
     </row>
     <row r="12" ht="62.5" customHeight="1" spans="1:14">
-      <c r="F12" s="68" t="s">
+      <c r="F12" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="G12" s="68"/>
+      <c r="G12" s="69"/>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="59" t="s">
         <v>81</v>
       </c>
     </row>
@@ -5103,12 +5109,12 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="29"/>
+      <c r="A19" s="30"/>
       <c r="B19" s="15"/>
-      <c r="C19" s="29" t="s">
+      <c r="C19" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="29" t="s">
+      <c r="D19" s="30" t="s">
         <v>35</v>
       </c>
       <c r="E19" s="7" t="s">
@@ -5119,41 +5125,41 @@
       </c>
     </row>
     <row r="20" ht="42.75" spans="1:14">
-      <c r="A20" s="59" t="s">
+      <c r="A20" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="59" t="s">
+      <c r="B20" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="60" t="s">
         <v>39</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="60" t="s">
         <v>61</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="60" t="s">
         <v>85</v>
       </c>
-      <c r="G20" s="59" t="s">
+      <c r="G20" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="H20" s="59" t="s">
+      <c r="H20" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="I20" s="59" t="s">
+      <c r="I20" s="60" t="s">
         <v>69</v>
       </c>
-      <c r="J20" s="59" t="s">
+      <c r="J20" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="M20" s="69"/>
-      <c r="N20" s="69"/>
+      <c r="M20" s="70"/>
+      <c r="N20" s="70"/>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="59"/>
+      <c r="A21" s="60"/>
       <c r="B21" s="13">
         <v>46024</v>
       </c>
@@ -5184,39 +5190,39 @@
         <f>I21</f>
         <v>6684.93150684932</v>
       </c>
-      <c r="M21" s="69"/>
-      <c r="N21" s="69"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="70"/>
     </row>
     <row r="22" ht="42.75" spans="1:14">
-      <c r="A22" s="59" t="s">
+      <c r="A22" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="59" t="s">
+      <c r="B22" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="59" t="s">
+      <c r="C22" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E22" s="59"/>
-      <c r="F22" s="59" t="s">
+      <c r="E22" s="60"/>
+      <c r="F22" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="G22" s="59"/>
-      <c r="H22" s="59" t="s">
+      <c r="G22" s="60"/>
+      <c r="H22" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="I22" s="59" t="s">
+      <c r="I22" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="J22" s="59" t="s">
+      <c r="J22" s="60" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="23" spans="1:14">
-      <c r="A23" s="59"/>
+      <c r="A23" s="60"/>
       <c r="B23" s="13">
         <v>46267</v>
       </c>
@@ -5241,41 +5247,41 @@
         <f>C23*D23*H23/365</f>
         <v>7532.87671232877</v>
       </c>
-      <c r="J23" s="30">
+      <c r="J23" s="31">
         <f>I23</f>
         <v>7532.87671232877</v>
       </c>
     </row>
     <row r="24" ht="42.75" spans="1:14">
-      <c r="A24" s="59" t="s">
+      <c r="A24" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="59" t="s">
+      <c r="B24" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C24" s="59" t="s">
+      <c r="C24" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D24" s="59" t="s">
+      <c r="D24" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59" t="s">
+      <c r="E24" s="60"/>
+      <c r="F24" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="G24" s="59"/>
-      <c r="H24" s="59" t="s">
+      <c r="G24" s="60"/>
+      <c r="H24" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="I24" s="59" t="s">
+      <c r="I24" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="J24" s="59" t="s">
+      <c r="J24" s="60" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="59"/>
+      <c r="A25" s="60"/>
       <c r="B25" s="13">
         <v>46300</v>
       </c>
@@ -5306,35 +5312,35 @@
       </c>
     </row>
     <row r="26" ht="42.75" spans="1:14">
-      <c r="A26" s="59" t="s">
+      <c r="A26" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="B26" s="59" t="s">
+      <c r="B26" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="59" t="s">
+      <c r="C26" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D26" s="59" t="s">
+      <c r="D26" s="60" t="s">
         <v>60</v>
       </c>
-      <c r="E26" s="59"/>
-      <c r="F26" s="59" t="s">
+      <c r="E26" s="60"/>
+      <c r="F26" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="G26" s="59"/>
-      <c r="H26" s="59" t="s">
+      <c r="G26" s="60"/>
+      <c r="H26" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="I26" s="59" t="s">
+      <c r="I26" s="60" t="s">
         <v>53</v>
       </c>
-      <c r="J26" s="59" t="s">
+      <c r="J26" s="60" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="59"/>
+      <c r="A27" s="60"/>
       <c r="B27" s="13">
         <v>46386</v>
       </c>
@@ -5352,14 +5358,14 @@
       <c r="G27" s="15">
         <v>100</v>
       </c>
-      <c r="H27" s="66">
+      <c r="H27" s="67">
         <v>0.005</v>
       </c>
-      <c r="I27" s="70">
+      <c r="I27" s="71">
         <f>C27*D27*H27/365</f>
         <v>4390.41095890411</v>
       </c>
-      <c r="J27" s="30">
+      <c r="J27" s="31">
         <f t="shared" si="2"/>
         <v>4390.41095890411</v>
       </c>
@@ -5384,7 +5390,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X90"/>
+  <dimension ref="A1:X92"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="7.5" customWidth="1"/>
@@ -5393,18 +5399,18 @@
     <col min="4" max="4" width="20.25" customWidth="1"/>
     <col min="5" max="5" width="14.5" customWidth="1"/>
     <col min="6" max="6" width="13.5" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
+    <col min="7" max="7" width="9.875" customWidth="1"/>
     <col min="8" max="8" width="8.5" customWidth="1"/>
     <col min="9" max="9" width="12.5" customWidth="1"/>
     <col min="10" max="10" width="11" customWidth="1"/>
     <col min="12" max="12" width="9.625" customWidth="1"/>
     <col min="13" max="13" width="13.5" customWidth="1"/>
-    <col min="14" max="14" width="14.625" customWidth="1"/>
+    <col min="14" max="14" width="17.375" customWidth="1"/>
     <col min="15" max="15" width="12.125" customWidth="1"/>
     <col min="16" max="16" width="9.625" customWidth="1"/>
     <col min="17" max="17" width="8" customWidth="1"/>
     <col min="18" max="18" width="8.5" customWidth="1"/>
-    <col min="19" max="19" width="15.875" customWidth="1"/>
+    <col min="19" max="19" width="19" customWidth="1"/>
     <col min="20" max="20" width="13" customWidth="1"/>
     <col min="21" max="21" width="11.875" customWidth="1"/>
     <col min="22" max="22" width="13.375" customWidth="1"/>
@@ -5442,7 +5448,7 @@
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
     </row>
-    <row r="2" ht="28.5" spans="1:24">
+    <row r="2" ht="15" spans="1:24">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="6" t="s">
@@ -5451,9 +5457,7 @@
       <c r="D2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="E2" s="4"/>
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
@@ -5478,7 +5482,7 @@
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
     </row>
-    <row r="3" ht="30" spans="1:24">
+    <row r="3" ht="15" spans="1:24">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -5493,12 +5497,8 @@
       </c>
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>37</v>
-      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="2"/>
@@ -5511,16 +5511,10 @@
       <c r="N3" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="O3" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="O3" s="7"/>
       <c r="P3" s="7"/>
-      <c r="Q3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="R3" s="7" t="s">
-        <v>37</v>
-      </c>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
@@ -5528,7 +5522,7 @@
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
     </row>
-    <row r="4" ht="57" spans="1:24">
+    <row r="4" ht="42.75" spans="1:24">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -5595,55 +5589,56 @@
     <row r="5" ht="15" spans="1:24">
       <c r="A5" s="12"/>
       <c r="B5" s="13">
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="C5" s="14">
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="D5" s="15">
         <f>F5-E5+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E5" s="13">
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="F5" s="16">
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="G5" s="15">
         <v>80</v>
       </c>
       <c r="H5" s="17">
+        <f>IF(G5&lt;60,0%,IF(G5&lt;=64,2.5%,IF(G5&lt;=69,2.25%,IF(G5&lt;=74,2%,IF(G5&lt;=79,1.75%,IF(G5&lt;=84,1.5%,IF(G5&lt;=89,1.25%,IF(G5&lt;=94,1%,IF(G5&lt;=97,0.75%,IF(G5&lt;=100,0.5%,""))))))))))</f>
         <v>0.015</v>
       </c>
       <c r="I5" s="18">
         <f>C5*H5*D5/365</f>
-        <v>15041.095890411</v>
-      </c>
-      <c r="J5" s="14">
+        <v>178356.164383562</v>
+      </c>
+      <c r="J5" s="18">
         <f>I5</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="13">
         <f t="shared" ref="L5:R5" si="0">B5</f>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="M5" s="14">
         <f t="shared" si="0"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N5" s="15">
         <f>P5-O5+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O5" s="13">
         <f t="shared" si="0"/>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="P5" s="16">
         <f t="shared" si="0"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q5" s="15">
         <f t="shared" si="0"/>
@@ -5655,7 +5650,7 @@
       </c>
       <c r="S5" s="19">
         <f>M5*N5*R5/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="T5" s="14">
         <v>0</v>
@@ -5665,7 +5660,7 @@
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
     </row>
-    <row r="6" ht="57" spans="1:24">
+    <row r="6" ht="42.75" spans="1:24">
       <c r="A6" s="10" t="s">
         <v>47</v>
       </c>
@@ -5736,55 +5731,58 @@
     <row r="7" ht="15" spans="1:24">
       <c r="A7" s="12"/>
       <c r="B7" s="13">
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="C7" s="14">
-        <v>1000000</v>
+        <f>C5</f>
+        <v>10000000</v>
       </c>
       <c r="D7" s="20">
         <f>F7-E5+1</f>
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="E7" s="16">
-        <v>46275</v>
+        <v>46583</v>
       </c>
       <c r="F7" s="21">
-        <v>46640</v>
+        <v>46664</v>
       </c>
       <c r="G7" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H7" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
       <c r="I7" s="18">
         <f>C7*H7*D7/365</f>
-        <v>16315.0684931507</v>
+        <v>155342.465753425</v>
       </c>
       <c r="J7" s="18">
         <f>I7</f>
-        <v>16315.0684931507</v>
+        <v>155342.465753425</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="13">
         <f t="shared" ref="L7:R7" si="1">B7</f>
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="M7" s="14">
         <f t="shared" si="1"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N7" s="20">
         <f>P7-O5+1</f>
-        <v>397</v>
+        <v>378</v>
       </c>
       <c r="O7" s="16">
         <f t="shared" si="1"/>
-        <v>46275</v>
+        <v>46583</v>
       </c>
       <c r="P7" s="21">
         <f t="shared" si="1"/>
-        <v>46640</v>
+        <v>46664</v>
       </c>
       <c r="Q7" s="15">
         <f t="shared" si="1"/>
@@ -5796,27 +5794,27 @@
       </c>
       <c r="S7" s="19">
         <f>W7+X7</f>
-        <v>16315.0684931507</v>
+        <v>155342.465753425</v>
       </c>
       <c r="T7" s="22">
         <f>S7</f>
-        <v>16315.0684931507</v>
+        <v>155342.465753425</v>
       </c>
       <c r="U7" s="15">
         <f>L7-O5</f>
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="V7" s="15">
         <f>N7-U7</f>
-        <v>366</v>
+        <v>81</v>
       </c>
       <c r="W7" s="23">
         <f>M5*R7*U7/365</f>
-        <v>1273.97260273973</v>
+        <v>122054.794520548</v>
       </c>
       <c r="X7" s="23">
         <f>M7*R7*V7/365</f>
-        <v>15041.095890411</v>
+        <v>33287.6712328767</v>
       </c>
     </row>
     <row r="8" ht="15" spans="1:24">
@@ -5920,10 +5918,10 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="W11" s="24"/>
       <c r="X11" s="3"/>
     </row>
-    <row r="12" ht="28.5" spans="1:24">
+    <row r="12" ht="15" spans="1:24">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6" t="s">
@@ -5932,9 +5930,7 @@
       <c r="D12" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -5959,15 +5955,15 @@
       <c r="W12" s="7"/>
       <c r="X12" s="7"/>
     </row>
-    <row r="13" ht="28.5" spans="1:24">
-      <c r="A13" s="24">
+    <row r="13" ht="15" spans="1:24">
+      <c r="A13" s="25">
         <v>2</v>
       </c>
-      <c r="B13" s="25"/>
-      <c r="C13" s="24" t="s">
+      <c r="B13" s="26"/>
+      <c r="C13" s="25" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="25" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="4"/>
@@ -5980,11 +5976,11 @@
       <c r="L13" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M13" s="8" t="s">
+      <c r="M13" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="N13" s="25" t="s">
         <v>34</v>
-      </c>
-      <c r="N13" s="8" t="s">
-        <v>35</v>
       </c>
       <c r="O13" s="7"/>
       <c r="P13" s="7"/>
@@ -5997,7 +5993,7 @@
       <c r="W13" s="7"/>
       <c r="X13" s="7"/>
     </row>
-    <row r="14" ht="57" spans="1:24">
+    <row r="14" ht="42.75" spans="1:24">
       <c r="A14" s="11" t="s">
         <v>38</v>
       </c>
@@ -6064,55 +6060,61 @@
     <row r="15" ht="15" spans="1:24">
       <c r="A15" s="11"/>
       <c r="B15" s="13">
-        <v>46244</v>
+        <f>B5</f>
+        <v>46287</v>
       </c>
       <c r="C15" s="14">
-        <v>1000000</v>
+        <f>C5</f>
+        <v>10000000</v>
       </c>
       <c r="D15" s="15">
         <f>F15-E15+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E15" s="13">
-        <v>46244</v>
+        <f>E5</f>
+        <v>46287</v>
       </c>
       <c r="F15" s="16">
-        <v>46609</v>
+        <f>F5</f>
+        <v>46720</v>
       </c>
       <c r="G15" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H15" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="27">
         <f>C15*H15*D15/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="J15" s="18">
         <f>I15</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="K15" s="2"/>
       <c r="L15" s="13">
         <f t="shared" ref="L15:R15" si="2">B15</f>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="M15" s="14">
         <f t="shared" si="2"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N15" s="15">
         <f>P15-O15+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O15" s="13">
         <f t="shared" si="2"/>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="P15" s="16">
         <f t="shared" si="2"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q15" s="15">
         <f t="shared" si="2"/>
@@ -6124,7 +6126,7 @@
       </c>
       <c r="S15" s="19">
         <f>M15*N15*R15/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="T15" s="14">
         <v>0</v>
@@ -6134,7 +6136,7 @@
       <c r="W15" s="7"/>
       <c r="X15" s="7"/>
     </row>
-    <row r="16" ht="57" spans="1:24">
+    <row r="16" ht="42.75" spans="1:24">
       <c r="A16" s="11" t="s">
         <v>47</v>
       </c>
@@ -6160,7 +6162,7 @@
       <c r="I16" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J16" s="27" t="s">
+      <c r="J16" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K16" s="2"/>
@@ -6205,55 +6207,60 @@
     <row r="17" ht="15" spans="1:24">
       <c r="A17" s="11"/>
       <c r="B17" s="13">
-        <v>46275</v>
+        <f>B7</f>
+        <v>46584</v>
       </c>
       <c r="C17" s="14">
-        <v>1500000</v>
+        <v>15000000</v>
       </c>
       <c r="D17" s="20">
         <f>F17-E15+1</f>
-        <v>366</v>
-      </c>
-      <c r="E17" s="28">
-        <v>46204</v>
+        <v>434</v>
+      </c>
+      <c r="E17" s="29">
+        <f>E7</f>
+        <v>46583</v>
       </c>
       <c r="F17" s="16">
-        <v>46609</v>
+        <f>F15</f>
+        <v>46720</v>
       </c>
       <c r="G17" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H17" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
-      <c r="I17" s="26">
+      <c r="I17" s="27">
         <f>C17*H17*D17/365</f>
-        <v>22561.6438356164</v>
-      </c>
-      <c r="J17" s="26">
+        <v>267534.246575342</v>
+      </c>
+      <c r="J17" s="27">
         <f>I17</f>
-        <v>22561.6438356164</v>
+        <v>267534.246575342</v>
       </c>
       <c r="K17" s="2"/>
       <c r="L17" s="13">
         <f t="shared" ref="L17:R17" si="3">B17</f>
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="M17" s="14">
         <f t="shared" si="3"/>
-        <v>1500000</v>
+        <v>15000000</v>
       </c>
       <c r="N17" s="20">
         <f>P17-O15+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O17" s="16">
         <f t="shared" si="3"/>
-        <v>46204</v>
+        <v>46583</v>
       </c>
       <c r="P17" s="21">
         <f t="shared" si="3"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q17" s="15">
         <f t="shared" si="3"/>
@@ -6265,27 +6272,27 @@
       </c>
       <c r="S17" s="19">
         <f>W17+X17</f>
-        <v>21924.6575342466</v>
+        <v>206506.849315069</v>
       </c>
       <c r="T17" s="22">
         <f>S17</f>
-        <v>21924.6575342466</v>
+        <v>206506.849315069</v>
       </c>
       <c r="U17" s="15">
         <f>L17-O15</f>
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="V17" s="15">
         <f>N17-U17</f>
-        <v>335</v>
+        <v>137</v>
       </c>
       <c r="W17" s="23">
         <f>M15*R17*U17/365</f>
-        <v>1273.97260273973</v>
+        <v>122054.794520548</v>
       </c>
       <c r="X17" s="23">
         <f>M17*R17*V17/365</f>
-        <v>20650.6849315069</v>
+        <v>84452.0547945205</v>
       </c>
     </row>
     <row r="18" ht="15" spans="1:24">
@@ -6392,7 +6399,7 @@
       <c r="W21" s="3"/>
       <c r="X21" s="3"/>
     </row>
-    <row r="22" ht="28.5" spans="1:24">
+    <row r="22" ht="15" spans="1:24">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
       <c r="C22" s="6" t="s">
@@ -6426,15 +6433,15 @@
       <c r="W22" s="7"/>
       <c r="X22" s="7"/>
     </row>
-    <row r="23" ht="28.5" spans="1:24">
-      <c r="A23" s="29">
+    <row r="23" ht="15" spans="1:24">
+      <c r="A23" s="30">
         <v>3</v>
       </c>
       <c r="B23" s="15"/>
-      <c r="C23" s="29" t="s">
+      <c r="C23" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D23" s="29" t="s">
+      <c r="D23" s="30" t="s">
         <v>35</v>
       </c>
       <c r="E23" s="4"/>
@@ -6464,7 +6471,7 @@
       <c r="W23" s="7"/>
       <c r="X23" s="7"/>
     </row>
-    <row r="24" ht="57" spans="1:24">
+    <row r="24" ht="42.75" spans="1:24">
       <c r="A24" s="11" t="s">
         <v>38</v>
       </c>
@@ -6531,55 +6538,61 @@
     <row r="25" ht="15" spans="1:24">
       <c r="A25" s="11"/>
       <c r="B25" s="13">
-        <v>46244</v>
+        <f>B5</f>
+        <v>46287</v>
       </c>
       <c r="C25" s="14">
-        <v>1000000</v>
+        <f>C5</f>
+        <v>10000000</v>
       </c>
       <c r="D25" s="15">
         <f>F25-E25+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E25" s="13">
-        <v>46244</v>
+        <f>E15</f>
+        <v>46287</v>
       </c>
       <c r="F25" s="16">
-        <v>46609</v>
+        <f>F15</f>
+        <v>46720</v>
       </c>
       <c r="G25" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H25" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
-      <c r="I25" s="26">
+      <c r="I25" s="27">
         <f>C25*H25*D25/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="J25" s="14">
         <f>I25</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="K25" s="2"/>
       <c r="L25" s="13">
         <f t="shared" ref="L25:R25" si="4">B25</f>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="M25" s="14">
         <f t="shared" si="4"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N25" s="15">
         <f>P25-O25+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O25" s="13">
         <f t="shared" si="4"/>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="P25" s="16">
         <f t="shared" si="4"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q25" s="15">
         <f t="shared" si="4"/>
@@ -6591,7 +6604,7 @@
       </c>
       <c r="S25" s="19">
         <f>M25*N25*R25/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="T25" s="14">
         <v>0</v>
@@ -6601,7 +6614,7 @@
       <c r="W25" s="7"/>
       <c r="X25" s="7"/>
     </row>
-    <row r="26" ht="57" spans="1:24">
+    <row r="26" ht="42.75" spans="1:24">
       <c r="A26" s="11" t="s">
         <v>47</v>
       </c>
@@ -6672,47 +6685,52 @@
     <row r="27" ht="15" spans="1:24">
       <c r="A27" s="11"/>
       <c r="B27" s="13">
-        <v>46275</v>
+        <f>B7</f>
+        <v>46584</v>
       </c>
       <c r="C27" s="14">
-        <v>1500000</v>
+        <f>C17</f>
+        <v>15000000</v>
       </c>
       <c r="D27" s="20">
         <f>F27-E25+1</f>
-        <v>329</v>
+        <v>378</v>
       </c>
       <c r="E27" s="16">
         <v>46204</v>
       </c>
       <c r="F27" s="21">
-        <v>46572</v>
+        <f>F7</f>
+        <v>46664</v>
       </c>
       <c r="G27" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H27" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
       <c r="I27" s="18">
         <f>C27*H27*D27/365</f>
-        <v>20280.8219178082</v>
-      </c>
-      <c r="J27" s="26">
+        <v>233013.698630137</v>
+      </c>
+      <c r="J27" s="27">
         <f>I27</f>
-        <v>20280.8219178082</v>
+        <v>233013.698630137</v>
       </c>
       <c r="K27" s="2"/>
       <c r="L27" s="13">
         <f t="shared" ref="L27:R27" si="5">B27</f>
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="M27" s="14">
         <f t="shared" si="5"/>
-        <v>1500000</v>
+        <v>15000000</v>
       </c>
       <c r="N27" s="20">
         <f>P27-O25+1</f>
-        <v>329</v>
+        <v>378</v>
       </c>
       <c r="O27" s="16">
         <f t="shared" si="5"/>
@@ -6720,7 +6738,7 @@
       </c>
       <c r="P27" s="21">
         <f t="shared" si="5"/>
-        <v>46572</v>
+        <v>46664</v>
       </c>
       <c r="Q27" s="15">
         <f t="shared" si="5"/>
@@ -6732,27 +6750,27 @@
       </c>
       <c r="S27" s="19">
         <f>W27+X27</f>
-        <v>19643.8356164384</v>
+        <v>171986.301369863</v>
       </c>
       <c r="T27" s="22">
         <f>S27</f>
-        <v>19643.8356164384</v>
+        <v>171986.301369863</v>
       </c>
       <c r="U27" s="15">
         <f>L27-O25</f>
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="V27" s="15">
         <f>N27-U27</f>
-        <v>298</v>
+        <v>81</v>
       </c>
       <c r="W27" s="23">
         <f>M25*R27*U27/365</f>
-        <v>1273.97260273973</v>
+        <v>122054.794520548</v>
       </c>
       <c r="X27" s="23">
         <f>M27*R27*V27/365</f>
-        <v>18369.8630136986</v>
+        <v>49931.5068493151</v>
       </c>
     </row>
     <row r="28" ht="15" spans="1:24">
@@ -6885,7 +6903,7 @@
       <c r="W32" s="3"/>
       <c r="X32" s="3"/>
     </row>
-    <row r="33" ht="28.5" spans="1:24">
+    <row r="33" ht="15" spans="1:24">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
       <c r="C33" s="6" t="s">
@@ -6894,9 +6912,7 @@
       <c r="D33" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
@@ -6921,15 +6937,15 @@
       <c r="W33" s="7"/>
       <c r="X33" s="7"/>
     </row>
-    <row r="34" ht="28.5" spans="1:24">
-      <c r="A34" s="24">
+    <row r="34" ht="15" spans="1:24">
+      <c r="A34" s="25">
         <v>4</v>
       </c>
-      <c r="B34" s="25"/>
-      <c r="C34" s="24" t="s">
+      <c r="B34" s="26"/>
+      <c r="C34" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="25" t="s">
         <v>54</v>
       </c>
       <c r="E34" s="4"/>
@@ -6959,7 +6975,7 @@
       <c r="W34" s="7"/>
       <c r="X34" s="7"/>
     </row>
-    <row r="35" ht="57" spans="1:24">
+    <row r="35" ht="42.75" spans="1:24">
       <c r="A35" s="11" t="s">
         <v>38</v>
       </c>
@@ -7026,55 +7042,61 @@
     <row r="36" ht="15" spans="1:24">
       <c r="A36" s="11"/>
       <c r="B36" s="13">
-        <v>46244</v>
+        <f>B5</f>
+        <v>46287</v>
       </c>
       <c r="C36" s="14">
-        <v>1000000</v>
+        <f>C25</f>
+        <v>10000000</v>
       </c>
       <c r="D36" s="15">
         <f>F36-E36+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E36" s="13">
-        <v>46244</v>
+        <f>E25</f>
+        <v>46287</v>
       </c>
       <c r="F36" s="16">
-        <v>46609</v>
+        <f>F25</f>
+        <v>46720</v>
       </c>
       <c r="G36" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H36" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
-      <c r="I36" s="26">
+      <c r="I36" s="27">
         <f>C36*H36*D36/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="J36" s="14">
         <f>I36</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="13">
         <f t="shared" ref="L36:R36" si="6">B36</f>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="M36" s="14">
         <f t="shared" si="6"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N36" s="15">
         <f>P36-O36+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O36" s="13">
         <f t="shared" si="6"/>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="P36" s="16">
         <f t="shared" si="6"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q36" s="15">
         <f t="shared" si="6"/>
@@ -7086,7 +7108,7 @@
       </c>
       <c r="S36" s="19">
         <f>M36*N36*R36/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="T36" s="14">
         <v>0</v>
@@ -7096,7 +7118,7 @@
       <c r="W36" s="7"/>
       <c r="X36" s="7"/>
     </row>
-    <row r="37" ht="57" spans="1:24">
+    <row r="37" ht="42.75" spans="1:24">
       <c r="A37" s="11" t="s">
         <v>47</v>
       </c>
@@ -7122,7 +7144,7 @@
       <c r="I37" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J37" s="27" t="s">
+      <c r="J37" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K37" s="2"/>
@@ -7167,14 +7189,15 @@
     <row r="38" ht="15" spans="1:24">
       <c r="A38" s="11"/>
       <c r="B38" s="13">
-        <v>46275</v>
+        <f>B7</f>
+        <v>46584</v>
       </c>
       <c r="C38" s="14">
         <v>1000000</v>
       </c>
       <c r="D38" s="20">
         <f>F38-E36+1</f>
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="E38" s="16">
         <v>46204</v>
@@ -7183,23 +7206,25 @@
         <v>46450</v>
       </c>
       <c r="G38" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H38" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
       <c r="I38" s="18">
         <f>C38*H38*D38/365</f>
-        <v>8506.84931506849</v>
-      </c>
-      <c r="J38" s="30">
+        <v>6739.72602739726</v>
+      </c>
+      <c r="J38" s="31">
         <f>I38</f>
-        <v>8506.84931506849</v>
+        <v>6739.72602739726</v>
       </c>
       <c r="K38" s="2"/>
       <c r="L38" s="13">
         <f t="shared" ref="L38:R38" si="7">B38</f>
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="M38" s="14">
         <f t="shared" si="7"/>
@@ -7207,7 +7232,7 @@
       </c>
       <c r="N38" s="20">
         <f>P38-O36+1</f>
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="O38" s="16">
         <f t="shared" si="7"/>
@@ -7227,27 +7252,27 @@
       </c>
       <c r="S38" s="19">
         <f>W38+X38</f>
-        <v>8506.84931506849</v>
+        <v>116589.04109589</v>
       </c>
       <c r="T38" s="22">
         <f>S38</f>
-        <v>8506.84931506849</v>
+        <v>116589.04109589</v>
       </c>
       <c r="U38" s="15">
         <f>L38-O36</f>
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="V38" s="15">
         <f>N38-U38</f>
-        <v>176</v>
+        <v>-133</v>
       </c>
       <c r="W38" s="23">
         <f>M36*R38*U38/365</f>
-        <v>1273.97260273973</v>
+        <v>122054.794520548</v>
       </c>
       <c r="X38" s="23">
         <f>M38*R38*V38/365</f>
-        <v>7232.87671232877</v>
+        <v>-5465.75342465753</v>
       </c>
     </row>
     <row r="39" ht="15" spans="1:24">
@@ -7260,7 +7285,7 @@
       <c r="G39" s="4"/>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="31"/>
+      <c r="J39" s="32"/>
       <c r="K39" s="2"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
@@ -7354,7 +7379,7 @@
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
     </row>
-    <row r="43" ht="28.5" spans="1:24">
+    <row r="43" ht="15" spans="1:24">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
       <c r="C43" s="6" t="s">
@@ -7363,9 +7388,7 @@
       <c r="D43" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E43" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="4"/>
       <c r="H43" s="4"/>
@@ -7391,14 +7414,14 @@
       <c r="X43" s="7"/>
     </row>
     <row r="44" ht="15" spans="1:24">
-      <c r="A44" s="24">
+      <c r="A44" s="25">
         <v>5</v>
       </c>
-      <c r="B44" s="25"/>
-      <c r="C44" s="29" t="s">
+      <c r="B44" s="26"/>
+      <c r="C44" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="D44" s="29" t="s">
+      <c r="D44" s="30" t="s">
         <v>54</v>
       </c>
       <c r="E44" s="4"/>
@@ -7411,10 +7434,10 @@
       <c r="L44" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M44" s="29" t="s">
+      <c r="M44" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="N44" s="29" t="s">
+      <c r="N44" s="30" t="s">
         <v>54</v>
       </c>
       <c r="O44" s="7"/>
@@ -7428,7 +7451,7 @@
       <c r="W44" s="7"/>
       <c r="X44" s="7"/>
     </row>
-    <row r="45" ht="57" spans="1:24">
+    <row r="45" ht="42.75" spans="1:24">
       <c r="A45" s="11" t="s">
         <v>38</v>
       </c>
@@ -7495,55 +7518,61 @@
     <row r="46" ht="15" spans="1:24">
       <c r="A46" s="11"/>
       <c r="B46" s="13">
-        <v>46244</v>
+        <f>B5</f>
+        <v>46287</v>
       </c>
       <c r="C46" s="14">
-        <v>1000000</v>
+        <f>C36</f>
+        <v>10000000</v>
       </c>
       <c r="D46" s="15">
         <f>F46-E46+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E46" s="13">
-        <v>46244</v>
+        <f>E36</f>
+        <v>46287</v>
       </c>
       <c r="F46" s="16">
-        <v>46609</v>
+        <f>F36</f>
+        <v>46720</v>
       </c>
       <c r="G46" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H46" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
-      <c r="I46" s="26">
+      <c r="I46" s="27">
         <f>C46*H46*D46/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="J46" s="14">
         <f>I46</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="K46" s="2"/>
       <c r="L46" s="13">
         <f t="shared" ref="L46:R46" si="8">B46</f>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="M46" s="14">
         <f t="shared" si="8"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N46" s="15">
         <f>P46-O46+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O46" s="13">
         <f t="shared" si="8"/>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="P46" s="16">
         <f t="shared" si="8"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q46" s="15">
         <f t="shared" si="8"/>
@@ -7555,7 +7584,7 @@
       </c>
       <c r="S46" s="19">
         <f>M46*N46*R46/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="T46" s="14">
         <v>0</v>
@@ -7565,7 +7594,7 @@
       <c r="W46" s="7"/>
       <c r="X46" s="7"/>
     </row>
-    <row r="47" ht="57" spans="1:24">
+    <row r="47" ht="42.75" spans="1:24">
       <c r="A47" s="11" t="s">
         <v>47</v>
       </c>
@@ -7591,7 +7620,7 @@
       <c r="I47" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J47" s="27" t="s">
+      <c r="J47" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K47" s="2"/>
@@ -7636,14 +7665,15 @@
     <row r="48" ht="15" spans="1:24">
       <c r="A48" s="11"/>
       <c r="B48" s="13">
-        <v>46275</v>
+        <f>B7</f>
+        <v>46584</v>
       </c>
       <c r="C48" s="14">
         <v>1500000</v>
       </c>
       <c r="D48" s="20">
         <f>F48-E46+1</f>
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="E48" s="16">
         <v>46204</v>
@@ -7652,23 +7682,25 @@
         <v>46450</v>
       </c>
       <c r="G48" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H48" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
       <c r="I48" s="18">
         <f>C48*H48*D48/365</f>
-        <v>12760.2739726027</v>
-      </c>
-      <c r="J48" s="30">
+        <v>10109.5890410959</v>
+      </c>
+      <c r="J48" s="31">
         <f>I48</f>
-        <v>12760.2739726027</v>
+        <v>10109.5890410959</v>
       </c>
       <c r="K48" s="2"/>
       <c r="L48" s="13">
         <f t="shared" ref="L48:R48" si="9">B48</f>
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="M48" s="14">
         <f t="shared" si="9"/>
@@ -7676,7 +7708,7 @@
       </c>
       <c r="N48" s="20">
         <f>P48-O46+1</f>
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="O48" s="16">
         <f t="shared" si="9"/>
@@ -7696,27 +7728,27 @@
       </c>
       <c r="S48" s="19">
         <f>W48+X48</f>
-        <v>12123.2876712329</v>
+        <v>113856.164383562</v>
       </c>
       <c r="T48" s="22">
         <f>S48</f>
-        <v>12123.2876712329</v>
+        <v>113856.164383562</v>
       </c>
       <c r="U48" s="15">
         <f>L48-O46</f>
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="V48" s="15">
         <f>N48-U48</f>
-        <v>176</v>
+        <v>-133</v>
       </c>
       <c r="W48" s="23">
         <f>M46*R48*U48/365</f>
-        <v>1273.97260273973</v>
+        <v>122054.794520548</v>
       </c>
       <c r="X48" s="23">
         <f>M48*R48*V48/365</f>
-        <v>10849.3150684932</v>
+        <v>-8198.6301369863</v>
       </c>
     </row>
     <row r="49" spans="1:24">
@@ -7797,7 +7829,7 @@
       <c r="W51" s="3"/>
       <c r="X51" s="3"/>
     </row>
-    <row r="52" ht="28.5" spans="1:24">
+    <row r="52" ht="15" spans="1:24">
       <c r="A52" s="4"/>
       <c r="B52" s="5"/>
       <c r="C52" s="6" t="s">
@@ -7834,14 +7866,14 @@
       <c r="X52" s="7"/>
     </row>
     <row r="53" ht="15" spans="1:24">
-      <c r="A53" s="24">
+      <c r="A53" s="25">
         <v>6</v>
       </c>
-      <c r="B53" s="25"/>
-      <c r="C53" s="29" t="s">
+      <c r="B53" s="26"/>
+      <c r="C53" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="29" t="s">
+      <c r="D53" s="30" t="s">
         <v>35</v>
       </c>
       <c r="E53" s="4"/>
@@ -7854,10 +7886,10 @@
       <c r="L53" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M53" s="29" t="s">
+      <c r="M53" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="N53" s="29" t="s">
+      <c r="N53" s="30" t="s">
         <v>35</v>
       </c>
       <c r="O53" s="7"/>
@@ -7871,7 +7903,7 @@
       <c r="W53" s="7"/>
       <c r="X53" s="7"/>
     </row>
-    <row r="54" ht="57" spans="1:24">
+    <row r="54" ht="42.75" spans="1:24">
       <c r="A54" s="11" t="s">
         <v>38</v>
       </c>
@@ -7938,55 +7970,61 @@
     <row r="55" ht="15" spans="1:24">
       <c r="A55" s="11"/>
       <c r="B55" s="13">
-        <v>46244</v>
+        <f>B5</f>
+        <v>46287</v>
       </c>
       <c r="C55" s="14">
-        <v>1000000</v>
+        <f>C46</f>
+        <v>10000000</v>
       </c>
       <c r="D55" s="15">
         <f>F55-E55+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E55" s="13">
-        <v>46244</v>
+        <f>E46</f>
+        <v>46287</v>
       </c>
       <c r="F55" s="16">
-        <v>46609</v>
+        <f>F46</f>
+        <v>46720</v>
       </c>
       <c r="G55" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H55" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
-      <c r="I55" s="26">
+      <c r="I55" s="27">
         <f>C55*H55*D55/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="J55" s="14">
         <f>I55</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="K55" s="2"/>
       <c r="L55" s="13">
         <f t="shared" ref="L55:R55" si="10">B55</f>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="M55" s="14">
         <f t="shared" si="10"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N55" s="15">
         <f>P55-O55+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O55" s="13">
         <f t="shared" si="10"/>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="P55" s="16">
         <f t="shared" si="10"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q55" s="15">
         <f t="shared" si="10"/>
@@ -7998,7 +8036,7 @@
       </c>
       <c r="S55" s="19">
         <f>M55*N55*R55/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="T55" s="14">
         <v>0</v>
@@ -8008,7 +8046,7 @@
       <c r="W55" s="7"/>
       <c r="X55" s="7"/>
     </row>
-    <row r="56" ht="57" spans="1:24">
+    <row r="56" ht="42.75" spans="1:24">
       <c r="A56" s="11" t="s">
         <v>47</v>
       </c>
@@ -8034,7 +8072,7 @@
       <c r="I56" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J56" s="27" t="s">
+      <c r="J56" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K56" s="2"/>
@@ -8079,14 +8117,15 @@
     <row r="57" ht="15" spans="1:24">
       <c r="A57" s="11"/>
       <c r="B57" s="13">
-        <v>46275</v>
+        <f>B7</f>
+        <v>46584</v>
       </c>
       <c r="C57" s="14">
         <v>900000</v>
       </c>
       <c r="D57" s="20">
         <f>F57-E55+1</f>
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="E57" s="16">
         <v>46204</v>
@@ -8095,23 +8134,25 @@
         <v>46572</v>
       </c>
       <c r="G57" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H57" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
       <c r="I57" s="18">
         <f>C57*H57*D57/365</f>
-        <v>12168.4931506849</v>
-      </c>
-      <c r="J57" s="30">
+        <v>10578.0821917808</v>
+      </c>
+      <c r="J57" s="31">
         <f>I57</f>
-        <v>12168.4931506849</v>
+        <v>10578.0821917808</v>
       </c>
       <c r="K57" s="2"/>
       <c r="L57" s="13">
         <f t="shared" ref="L57:R57" si="11">B57</f>
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="M57" s="14">
         <f t="shared" si="11"/>
@@ -8119,7 +8160,7 @@
       </c>
       <c r="N57" s="20">
         <f>P57-O55+1</f>
-        <v>329</v>
+        <v>286</v>
       </c>
       <c r="O57" s="16">
         <f t="shared" si="11"/>
@@ -8139,27 +8180,27 @@
       </c>
       <c r="S57" s="19">
         <f>W57+X57</f>
-        <v>12295.8904109589</v>
+        <v>121647.945205479</v>
       </c>
       <c r="T57" s="22">
         <f>S57</f>
-        <v>12295.8904109589</v>
+        <v>121647.945205479</v>
       </c>
       <c r="U57" s="15">
         <f>L57-O55</f>
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="V57" s="15">
         <f>N57-U57</f>
-        <v>298</v>
+        <v>-11</v>
       </c>
       <c r="W57" s="23">
         <f>M55*R57*U57/365</f>
-        <v>1273.97260273973</v>
+        <v>122054.794520548</v>
       </c>
       <c r="X57" s="23">
         <f>M57*R57*V57/365</f>
-        <v>11021.9178082192</v>
+        <v>-406.849315068493</v>
       </c>
     </row>
     <row r="58" spans="1:24">
@@ -8240,7 +8281,7 @@
       <c r="W60" s="3"/>
       <c r="X60" s="3"/>
     </row>
-    <row r="61" ht="28.5" spans="1:24">
+    <row r="61" ht="15" spans="1:24">
       <c r="A61" s="4"/>
       <c r="B61" s="5"/>
       <c r="C61" s="6" t="s">
@@ -8249,9 +8290,7 @@
       <c r="D61" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E61" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="4"/>
       <c r="H61" s="4"/>
@@ -8277,14 +8316,14 @@
       <c r="X61" s="7"/>
     </row>
     <row r="62" ht="15" spans="1:24">
-      <c r="A62" s="24">
+      <c r="A62" s="25">
         <v>7</v>
       </c>
-      <c r="B62" s="25"/>
-      <c r="C62" s="29" t="s">
+      <c r="B62" s="26"/>
+      <c r="C62" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="D62" s="30" t="s">
         <v>54</v>
       </c>
       <c r="E62" s="4"/>
@@ -8297,10 +8336,10 @@
       <c r="L62" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M62" s="29" t="s">
+      <c r="M62" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="N62" s="29" t="s">
+      <c r="N62" s="30" t="s">
         <v>54</v>
       </c>
       <c r="O62" s="7"/>
@@ -8314,7 +8353,7 @@
       <c r="W62" s="7"/>
       <c r="X62" s="7"/>
     </row>
-    <row r="63" ht="57" spans="1:24">
+    <row r="63" ht="42.75" spans="1:24">
       <c r="A63" s="11" t="s">
         <v>38</v>
       </c>
@@ -8381,55 +8420,61 @@
     <row r="64" ht="15" spans="1:24">
       <c r="A64" s="11"/>
       <c r="B64" s="13">
-        <v>46244</v>
+        <f>B5</f>
+        <v>46287</v>
       </c>
       <c r="C64" s="14">
-        <v>1000000</v>
+        <f>C55</f>
+        <v>10000000</v>
       </c>
       <c r="D64" s="15">
         <f>F64-E64+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E64" s="13">
-        <v>46244</v>
+        <f>E55</f>
+        <v>46287</v>
       </c>
       <c r="F64" s="16">
-        <v>46609</v>
+        <f>F55</f>
+        <v>46720</v>
       </c>
       <c r="G64" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H64" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
-      <c r="I64" s="26">
+      <c r="I64" s="27">
         <f>C64*H64*D64/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="J64" s="14">
         <f>I64</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="K64" s="2"/>
       <c r="L64" s="13">
         <f t="shared" ref="L64:R64" si="12">B64</f>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="M64" s="14">
         <f t="shared" si="12"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N64" s="15">
         <f>P64-O64+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O64" s="13">
         <f t="shared" si="12"/>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="P64" s="16">
         <f t="shared" si="12"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q64" s="15">
         <f t="shared" si="12"/>
@@ -8441,7 +8486,7 @@
       </c>
       <c r="S64" s="19">
         <f>M64*N64*R64/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="T64" s="14">
         <v>0</v>
@@ -8451,7 +8496,7 @@
       <c r="W64" s="7"/>
       <c r="X64" s="7"/>
     </row>
-    <row r="65" ht="57" spans="1:24">
+    <row r="65" ht="42.75" spans="1:24">
       <c r="A65" s="11" t="s">
         <v>47</v>
       </c>
@@ -8477,7 +8522,7 @@
       <c r="I65" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J65" s="27" t="s">
+      <c r="J65" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K65" s="2"/>
@@ -8522,14 +8567,15 @@
     <row r="66" ht="15" spans="1:24">
       <c r="A66" s="11"/>
       <c r="B66" s="13">
-        <v>46275</v>
+        <f>B7</f>
+        <v>46584</v>
       </c>
       <c r="C66" s="14">
         <v>900000</v>
       </c>
       <c r="D66" s="20">
         <f>F66-E64+1</f>
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="E66" s="16">
         <v>46204</v>
@@ -8538,23 +8584,25 @@
         <v>46450</v>
       </c>
       <c r="G66" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H66" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
       <c r="I66" s="18">
         <f>C66*H66*D66/365</f>
-        <v>7656.16438356164</v>
-      </c>
-      <c r="J66" s="30">
+        <v>6065.75342465753</v>
+      </c>
+      <c r="J66" s="31">
         <f>I66</f>
-        <v>7656.16438356164</v>
+        <v>6065.75342465753</v>
       </c>
       <c r="K66" s="2"/>
       <c r="L66" s="13">
         <f t="shared" ref="L66:R66" si="13">B66</f>
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="M66" s="14">
         <f t="shared" si="13"/>
@@ -8562,7 +8610,7 @@
       </c>
       <c r="N66" s="20">
         <f>P66-O64+1</f>
-        <v>207</v>
+        <v>164</v>
       </c>
       <c r="O66" s="16">
         <f t="shared" si="13"/>
@@ -8582,27 +8630,27 @@
       </c>
       <c r="S66" s="19">
         <f>W66+X66</f>
-        <v>7783.56164383562</v>
+        <v>117135.616438356</v>
       </c>
       <c r="T66" s="22">
         <f>S66</f>
-        <v>7783.56164383562</v>
+        <v>117135.616438356</v>
       </c>
       <c r="U66" s="15">
         <f>L66-O64</f>
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="V66" s="15">
         <f>N66-U66</f>
-        <v>176</v>
+        <v>-133</v>
       </c>
       <c r="W66" s="23">
         <f>M64*R66*U66/365</f>
-        <v>1273.97260273973</v>
+        <v>122054.794520548</v>
       </c>
       <c r="X66" s="23">
         <f>M66*R66*V66/365</f>
-        <v>6509.58904109589</v>
+        <v>-4919.17808219178</v>
       </c>
     </row>
     <row r="67" spans="1:24">
@@ -8683,7 +8731,7 @@
       <c r="W69" s="3"/>
       <c r="X69" s="3"/>
     </row>
-    <row r="70" ht="28.5" spans="1:24">
+    <row r="70" ht="15" spans="1:24">
       <c r="A70" s="4"/>
       <c r="B70" s="5"/>
       <c r="C70" s="6" t="s">
@@ -8692,9 +8740,7 @@
       <c r="D70" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E70" s="4" t="s">
-        <v>32</v>
-      </c>
+      <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="4"/>
       <c r="H70" s="4"/>
@@ -8720,14 +8766,14 @@
       <c r="X70" s="7"/>
     </row>
     <row r="71" ht="15" spans="1:24">
-      <c r="A71" s="24">
+      <c r="A71" s="25">
         <v>8</v>
       </c>
-      <c r="B71" s="25"/>
-      <c r="C71" s="29" t="s">
+      <c r="B71" s="26"/>
+      <c r="C71" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D71" s="30" t="s">
         <v>34</v>
       </c>
       <c r="E71" s="4"/>
@@ -8740,10 +8786,10 @@
       <c r="L71" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="M71" s="29" t="s">
+      <c r="M71" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="N71" s="29" t="s">
+      <c r="N71" s="30" t="s">
         <v>34</v>
       </c>
       <c r="O71" s="7"/>
@@ -8757,7 +8803,7 @@
       <c r="W71" s="7"/>
       <c r="X71" s="7"/>
     </row>
-    <row r="72" ht="57" spans="1:24">
+    <row r="72" ht="42.75" spans="1:24">
       <c r="A72" s="11" t="s">
         <v>38</v>
       </c>
@@ -8824,55 +8870,61 @@
     <row r="73" ht="15" spans="1:24">
       <c r="A73" s="11"/>
       <c r="B73" s="13">
-        <v>46244</v>
+        <f>B5</f>
+        <v>46287</v>
       </c>
       <c r="C73" s="14">
-        <v>1000000</v>
+        <f>C64</f>
+        <v>10000000</v>
       </c>
       <c r="D73" s="15">
         <f>F73-E73+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E73" s="13">
-        <v>46244</v>
+        <f>E64</f>
+        <v>46287</v>
       </c>
       <c r="F73" s="16">
-        <v>46609</v>
+        <f>F64</f>
+        <v>46720</v>
       </c>
       <c r="G73" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H73" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
-      <c r="I73" s="26">
+      <c r="I73" s="27">
         <f>C73*H73*D73/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="J73" s="14">
         <f>I73</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="K73" s="2"/>
       <c r="L73" s="13">
         <f t="shared" ref="L73:R73" si="14">B73</f>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="M73" s="14">
         <f t="shared" si="14"/>
-        <v>1000000</v>
+        <v>10000000</v>
       </c>
       <c r="N73" s="15">
         <f>P73-O73+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O73" s="13">
         <f t="shared" si="14"/>
-        <v>46244</v>
+        <v>46287</v>
       </c>
       <c r="P73" s="16">
         <f t="shared" si="14"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q73" s="15">
         <f t="shared" si="14"/>
@@ -8884,7 +8936,7 @@
       </c>
       <c r="S73" s="19">
         <f>M73*N73*R73/365</f>
-        <v>15041.095890411</v>
+        <v>178356.164383562</v>
       </c>
       <c r="T73" s="14">
         <v>0</v>
@@ -8894,7 +8946,7 @@
       <c r="W73" s="7"/>
       <c r="X73" s="7"/>
     </row>
-    <row r="74" ht="57" spans="1:24">
+    <row r="74" ht="42.75" spans="1:24">
       <c r="A74" s="11" t="s">
         <v>47</v>
       </c>
@@ -8920,7 +8972,7 @@
       <c r="I74" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="J74" s="27" t="s">
+      <c r="J74" s="28" t="s">
         <v>46</v>
       </c>
       <c r="K74" s="2"/>
@@ -8965,40 +9017,43 @@
     <row r="75" ht="15" spans="1:24">
       <c r="A75" s="11"/>
       <c r="B75" s="13">
-        <v>46275</v>
+        <f>B7</f>
+        <v>46584</v>
       </c>
       <c r="C75" s="14">
         <v>900000</v>
       </c>
       <c r="D75" s="20">
         <f>F75-E73+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="E75" s="16">
         <v>46204</v>
       </c>
       <c r="F75" s="21">
         <f>F73</f>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="G75" s="15">
+        <f>G5</f>
         <v>80</v>
       </c>
       <c r="H75" s="17">
+        <f>H5</f>
         <v>0.015</v>
       </c>
       <c r="I75" s="18">
         <f>C75*H75*D75/365</f>
-        <v>13536.9863013699</v>
-      </c>
-      <c r="J75" s="30">
+        <v>16052.0547945205</v>
+      </c>
+      <c r="J75" s="31">
         <f>I75</f>
-        <v>13536.9863013699</v>
+        <v>16052.0547945205</v>
       </c>
       <c r="K75" s="2"/>
       <c r="L75" s="13">
         <f t="shared" ref="L75:R75" si="15">B75</f>
-        <v>46275</v>
+        <v>46584</v>
       </c>
       <c r="M75" s="14">
         <f t="shared" si="15"/>
@@ -9006,7 +9061,7 @@
       </c>
       <c r="N75" s="20">
         <f>P75-O73+1</f>
-        <v>366</v>
+        <v>434</v>
       </c>
       <c r="O75" s="16">
         <f t="shared" si="15"/>
@@ -9014,7 +9069,7 @@
       </c>
       <c r="P75" s="21">
         <f t="shared" si="15"/>
-        <v>46609</v>
+        <v>46720</v>
       </c>
       <c r="Q75" s="15">
         <f t="shared" si="15"/>
@@ -9026,27 +9081,27 @@
       </c>
       <c r="S75" s="19">
         <f>W75+X75</f>
-        <v>13664.3835616438</v>
+        <v>127121.917808219</v>
       </c>
       <c r="T75" s="22">
         <f>S75</f>
-        <v>13664.3835616438</v>
+        <v>127121.917808219</v>
       </c>
       <c r="U75" s="15">
         <f>L75-O73</f>
-        <v>31</v>
+        <v>297</v>
       </c>
       <c r="V75" s="15">
         <f>N75-U75</f>
-        <v>335</v>
+        <v>137</v>
       </c>
       <c r="W75" s="23">
         <f>M73*R75*U75/365</f>
-        <v>1273.97260273973</v>
+        <v>122054.794520548</v>
       </c>
       <c r="X75" s="23">
         <f>M75*R75*V75/365</f>
-        <v>12390.4109589041</v>
+        <v>5067.12328767123</v>
       </c>
     </row>
     <row r="76" spans="1:24">
@@ -9154,10 +9209,10 @@
       <c r="X79" s="3"/>
     </row>
     <row r="80" spans="1:24">
-      <c r="A80" s="32"/>
-      <c r="B80" s="32"/>
-      <c r="C80" s="32"/>
-      <c r="D80" s="32"/>
+      <c r="A80" s="33"/>
+      <c r="B80" s="33"/>
+      <c r="C80" s="33"/>
+      <c r="D80" s="33"/>
       <c r="E80" s="3"/>
       <c r="F80" s="3"/>
       <c r="G80" s="3"/>
@@ -9179,7 +9234,7 @@
       <c r="W80" s="3"/>
       <c r="X80" s="3"/>
     </row>
-    <row r="81" ht="28.5" spans="1:24">
+    <row r="81" ht="15" spans="1:24">
       <c r="A81" s="7"/>
       <c r="B81" s="5"/>
       <c r="C81" s="6" t="s">
@@ -9194,7 +9249,7 @@
       <c r="H81" s="7"/>
       <c r="I81" s="7"/>
       <c r="J81" s="7"/>
-      <c r="K81" s="33"/>
+      <c r="K81" s="34"/>
       <c r="L81" s="5"/>
       <c r="M81" s="6" t="s">
         <v>31</v>
@@ -9214,646 +9269,805 @@
       <c r="X81" s="7"/>
     </row>
     <row r="82" ht="15" spans="1:24">
-      <c r="A82" s="34"/>
-      <c r="B82" s="35"/>
-      <c r="C82" s="34" t="s">
+      <c r="A82" s="35"/>
+      <c r="B82" s="36"/>
+      <c r="C82" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="D82" s="34" t="s">
+      <c r="D82" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="E82" s="36"/>
-      <c r="F82" s="36"/>
-      <c r="G82" s="36"/>
-      <c r="H82" s="36"/>
-      <c r="I82" s="36"/>
-      <c r="J82" s="36"/>
-      <c r="K82" s="37"/>
-      <c r="L82" s="35"/>
-      <c r="M82" s="34" t="s">
+      <c r="E82" s="37"/>
+      <c r="F82" s="37"/>
+      <c r="G82" s="37"/>
+      <c r="H82" s="37"/>
+      <c r="I82" s="37"/>
+      <c r="J82" s="37"/>
+      <c r="K82" s="38"/>
+      <c r="L82" s="36"/>
+      <c r="M82" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="N82" s="34" t="s">
+      <c r="N82" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="O82" s="36"/>
-      <c r="P82" s="36"/>
-      <c r="Q82" s="36"/>
-      <c r="R82" s="36"/>
-      <c r="S82" s="36"/>
-      <c r="T82" s="36"/>
-      <c r="U82" s="36"/>
-      <c r="V82" s="36"/>
-      <c r="W82" s="36"/>
-      <c r="X82" s="36"/>
+      <c r="O82" s="37"/>
+      <c r="P82" s="37"/>
+      <c r="Q82" s="37"/>
+      <c r="R82" s="37"/>
+      <c r="S82" s="37"/>
+      <c r="T82" s="37"/>
+      <c r="U82" s="37"/>
+      <c r="V82" s="37"/>
+      <c r="W82" s="37"/>
+      <c r="X82" s="37"/>
     </row>
     <row r="83" ht="57" spans="1:24">
-      <c r="A83" s="38" t="s">
+      <c r="A83" s="39" t="s">
         <v>38</v>
       </c>
-      <c r="B83" s="38" t="s">
+      <c r="B83" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="C83" s="38" t="s">
+      <c r="C83" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="D83" s="38" t="s">
+      <c r="D83" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="E83" s="38" t="s">
+      <c r="E83" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="F83" s="38" t="s">
+      <c r="F83" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="G83" s="38" t="s">
+      <c r="G83" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="H83" s="38" t="s">
+      <c r="H83" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="I83" s="38" t="s">
+      <c r="I83" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="J83" s="38" t="s">
+      <c r="J83" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="K83" s="37"/>
-      <c r="L83" s="38" t="s">
+      <c r="K83" s="38"/>
+      <c r="L83" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="M83" s="38" t="s">
+      <c r="M83" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="N83" s="38" t="s">
+      <c r="N83" s="39" t="s">
         <v>60</v>
       </c>
-      <c r="O83" s="38" t="s">
+      <c r="O83" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="P83" s="38" t="s">
+      <c r="P83" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="Q83" s="38" t="s">
+      <c r="Q83" s="39" t="s">
         <v>43</v>
       </c>
-      <c r="R83" s="38" t="s">
+      <c r="R83" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="S83" s="38" t="s">
+      <c r="S83" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="T83" s="38" t="s">
+      <c r="T83" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="U83" s="39"/>
-      <c r="V83" s="39"/>
-      <c r="W83" s="39"/>
-      <c r="X83" s="39"/>
+      <c r="U83" s="40"/>
+      <c r="V83" s="40"/>
+      <c r="W83" s="40"/>
+      <c r="X83" s="40"/>
     </row>
     <row r="84" ht="15" spans="1:24">
-      <c r="A84" s="38"/>
-      <c r="B84" s="40">
-        <v>46244</v>
-      </c>
-      <c r="C84" s="41">
-        <v>1000000</v>
-      </c>
-      <c r="D84" s="35">
+      <c r="A84" s="39"/>
+      <c r="B84" s="41">
+        <v>46288</v>
+      </c>
+      <c r="C84" s="42">
+        <v>10000000</v>
+      </c>
+      <c r="D84" s="36">
         <f>F84-E84+1</f>
-        <v>366</v>
-      </c>
-      <c r="E84" s="40">
-        <v>46244</v>
-      </c>
-      <c r="F84" s="42">
-        <v>46609</v>
-      </c>
-      <c r="G84" s="35">
-        <v>80</v>
-      </c>
-      <c r="H84" s="43">
-        <v>0.015</v>
-      </c>
-      <c r="I84" s="44">
+        <v>372</v>
+      </c>
+      <c r="E84" s="41">
+        <f>B84</f>
+        <v>46288</v>
+      </c>
+      <c r="F84" s="43">
+        <v>46659</v>
+      </c>
+      <c r="G84" s="36">
+        <v>70</v>
+      </c>
+      <c r="H84" s="44">
+        <f>IF(G84&lt;60,0%,IF(G84&lt;=64,2.5%,IF(G84&lt;=69,2.25%,IF(G84&lt;=74,2%,IF(G84&lt;=79,1.75%,IF(G84&lt;=84,1.5%,IF(G84&lt;=89,1.25%,IF(G84&lt;=94,1%,IF(G84&lt;=97,0.75%,IF(G84&lt;=100,0.5%,""))))))))))</f>
+        <v>0.02</v>
+      </c>
+      <c r="I84" s="45">
         <f t="shared" ref="I84:I88" si="16">C84*D84*H84/365</f>
-        <v>15041.095890411</v>
-      </c>
-      <c r="J84" s="41">
+        <v>203835.616438356</v>
+      </c>
+      <c r="J84" s="45">
         <f t="shared" ref="J84:J88" si="17">I84</f>
-        <v>15041.095890411</v>
-      </c>
-      <c r="K84" s="37"/>
-      <c r="L84" s="40">
+        <v>203835.616438356</v>
+      </c>
+      <c r="K84" s="38"/>
+      <c r="L84" s="41">
         <f t="shared" ref="L84:R84" si="18">B84</f>
-        <v>46244</v>
-      </c>
-      <c r="M84" s="41">
+        <v>46288</v>
+      </c>
+      <c r="M84" s="42">
         <f t="shared" si="18"/>
-        <v>1000000</v>
-      </c>
-      <c r="N84" s="35">
+        <v>10000000</v>
+      </c>
+      <c r="N84" s="36">
         <f>P84-O84+1</f>
-        <v>366</v>
-      </c>
-      <c r="O84" s="40">
+        <v>372</v>
+      </c>
+      <c r="O84" s="41">
         <f t="shared" si="18"/>
-        <v>46244</v>
-      </c>
-      <c r="P84" s="42">
+        <v>46288</v>
+      </c>
+      <c r="P84" s="43">
         <f t="shared" si="18"/>
-        <v>46609</v>
-      </c>
-      <c r="Q84" s="35">
+        <v>46659</v>
+      </c>
+      <c r="Q84" s="36">
         <f t="shared" si="18"/>
-        <v>80</v>
-      </c>
-      <c r="R84" s="43">
+        <v>70</v>
+      </c>
+      <c r="R84" s="44">
         <f t="shared" si="18"/>
-        <v>0.015</v>
-      </c>
-      <c r="S84" s="44">
+        <v>0.02</v>
+      </c>
+      <c r="S84" s="45">
         <f>M84*N84*R84/365</f>
-        <v>15041.095890411</v>
-      </c>
-      <c r="T84" s="41">
+        <v>203835.616438356</v>
+      </c>
+      <c r="T84" s="42">
         <v>0</v>
       </c>
-      <c r="U84" s="39"/>
-      <c r="V84" s="39"/>
-      <c r="W84" s="39"/>
-      <c r="X84" s="39"/>
-    </row>
-    <row r="85" ht="57" spans="1:24">
-      <c r="A85" s="38" t="s">
+      <c r="U84" s="40"/>
+      <c r="V84" s="40"/>
+      <c r="W84" s="40"/>
+      <c r="X84" s="40"/>
+    </row>
+    <row r="85" ht="42.75" spans="1:24">
+      <c r="A85" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="B85" s="38" t="s">
+      <c r="B85" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C85" s="38" t="s">
+      <c r="C85" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="D85" s="38" t="s">
+      <c r="D85" s="39" t="s">
         <v>60</v>
       </c>
       <c r="E85" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F85" s="38" t="s">
+      <c r="F85" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="G85" s="38"/>
-      <c r="H85" s="38" t="s">
+      <c r="G85" s="39"/>
+      <c r="H85" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="I85" s="38" t="s">
+      <c r="I85" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="J85" s="38" t="s">
+      <c r="J85" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="K85" s="37"/>
-      <c r="L85" s="38" t="s">
+      <c r="K85" s="38"/>
+      <c r="L85" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="M85" s="38" t="s">
+      <c r="M85" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="N85" s="38" t="s">
+      <c r="N85" s="39" t="s">
         <v>60</v>
       </c>
       <c r="O85" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="P85" s="38" t="s">
+      <c r="P85" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="Q85" s="38"/>
-      <c r="R85" s="38" t="s">
+      <c r="Q85" s="39"/>
+      <c r="R85" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="S85" s="38" t="s">
+      <c r="S85" s="39" t="s">
         <v>77</v>
       </c>
-      <c r="T85" s="38" t="s">
+      <c r="T85" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="U85" s="38" t="s">
+      <c r="U85" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="V85" s="38" t="s">
+      <c r="V85" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="W85" s="38" t="s">
+      <c r="W85" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="X85" s="38" t="s">
+      <c r="X85" s="39" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="86" ht="15" spans="1:24">
-      <c r="A86" s="38"/>
-      <c r="B86" s="40">
-        <v>46275</v>
-      </c>
-      <c r="C86" s="41">
-        <v>900000</v>
-      </c>
-      <c r="D86" s="45">
+      <c r="A86" s="39"/>
+      <c r="B86" s="41">
+        <v>46386</v>
+      </c>
+      <c r="C86" s="42">
+        <f>C84</f>
+        <v>10000000</v>
+      </c>
+      <c r="D86" s="46">
         <f>F86-E84+1</f>
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="E86" s="16">
         <v>46204</v>
       </c>
-      <c r="F86" s="42">
-        <v>46640</v>
-      </c>
-      <c r="G86" s="35">
-        <f t="shared" ref="G86:G90" si="19">G84</f>
-        <v>80</v>
-      </c>
-      <c r="H86" s="43">
-        <f t="shared" ref="H86:H90" si="20">H84</f>
-        <v>0.015</v>
-      </c>
-      <c r="I86" s="44">
+      <c r="F86" s="43">
+        <v>46664</v>
+      </c>
+      <c r="G86" s="36">
+        <f>G84</f>
+        <v>70</v>
+      </c>
+      <c r="H86" s="44">
+        <f t="shared" ref="H86:H90" si="19">H84</f>
+        <v>0.02</v>
+      </c>
+      <c r="I86" s="45">
         <f t="shared" si="16"/>
-        <v>14683.5616438356</v>
-      </c>
-      <c r="J86" s="46">
+        <v>206575.342465753</v>
+      </c>
+      <c r="J86" s="47">
         <f t="shared" si="17"/>
-        <v>14683.5616438356</v>
-      </c>
-      <c r="K86" s="37"/>
-      <c r="L86" s="40">
-        <f t="shared" ref="L86:R86" si="21">B86</f>
-        <v>46275</v>
-      </c>
-      <c r="M86" s="41">
-        <f t="shared" si="21"/>
-        <v>900000</v>
-      </c>
-      <c r="N86" s="45">
+        <v>206575.342465753</v>
+      </c>
+      <c r="K86" s="38"/>
+      <c r="L86" s="41">
+        <f t="shared" ref="L86:R86" si="20">B86</f>
+        <v>46386</v>
+      </c>
+      <c r="M86" s="42">
+        <f>M84</f>
+        <v>10000000</v>
+      </c>
+      <c r="N86" s="46">
         <f>P86-O84+1</f>
-        <v>397</v>
-      </c>
-      <c r="O86" s="47">
-        <f t="shared" si="21"/>
+        <v>377</v>
+      </c>
+      <c r="O86" s="48">
+        <f t="shared" si="20"/>
         <v>46204</v>
       </c>
-      <c r="P86" s="42">
-        <f t="shared" si="21"/>
-        <v>46640</v>
-      </c>
-      <c r="Q86" s="35">
-        <f t="shared" si="21"/>
-        <v>80</v>
-      </c>
-      <c r="R86" s="43">
-        <f t="shared" si="21"/>
-        <v>0.015</v>
-      </c>
-      <c r="S86" s="48">
-        <f t="shared" ref="S86:S90" si="22">W86+X86</f>
-        <v>14810.9589041096</v>
-      </c>
-      <c r="T86" s="49">
+      <c r="P86" s="43">
+        <f t="shared" si="20"/>
+        <v>46664</v>
+      </c>
+      <c r="Q86" s="36">
+        <f t="shared" si="20"/>
+        <v>70</v>
+      </c>
+      <c r="R86" s="44">
+        <f t="shared" si="20"/>
+        <v>0.02</v>
+      </c>
+      <c r="S86" s="49">
+        <f t="shared" ref="S86:S90" si="21">W86+X86</f>
+        <v>206575.342465753</v>
+      </c>
+      <c r="T86" s="50">
         <f>S86</f>
-        <v>14810.9589041096</v>
-      </c>
-      <c r="U86" s="50">
+        <v>206575.342465753</v>
+      </c>
+      <c r="U86" s="51">
         <f>L86-O84</f>
-        <v>31</v>
-      </c>
-      <c r="V86" s="50">
-        <f t="shared" ref="V86:V90" si="23">N86-U86</f>
-        <v>366</v>
-      </c>
-      <c r="W86" s="51">
+        <v>98</v>
+      </c>
+      <c r="V86" s="51">
+        <f t="shared" ref="V86:V90" si="22">N86-U86</f>
+        <v>279</v>
+      </c>
+      <c r="W86" s="52">
         <f>M84*R84*U86/365</f>
-        <v>1273.97260273973</v>
-      </c>
-      <c r="X86" s="52">
-        <f t="shared" ref="X86:X90" si="24">M86*R86*V86/365</f>
-        <v>13536.9863013699</v>
-      </c>
-    </row>
-    <row r="87" ht="57" spans="1:24">
-      <c r="A87" s="38" t="s">
+        <v>53698.6301369863</v>
+      </c>
+      <c r="X86" s="53">
+        <f t="shared" ref="X86:X90" si="23">M86*R86*V86/365</f>
+        <v>152876.712328767</v>
+      </c>
+    </row>
+    <row r="87" ht="42.75" spans="1:24">
+      <c r="A87" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="B87" s="38" t="s">
+      <c r="B87" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C87" s="38" t="s">
+      <c r="C87" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="D87" s="38" t="s">
+      <c r="D87" s="39" t="s">
         <v>60</v>
       </c>
       <c r="E87" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F87" s="38" t="s">
+      <c r="F87" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="G87" s="38"/>
-      <c r="H87" s="38" t="s">
+      <c r="G87" s="39"/>
+      <c r="H87" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="I87" s="38" t="s">
+      <c r="I87" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="J87" s="38" t="s">
+      <c r="J87" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="K87" s="37"/>
-      <c r="L87" s="38" t="s">
+      <c r="K87" s="38"/>
+      <c r="L87" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="M87" s="38" t="s">
+      <c r="M87" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="N87" s="38" t="s">
+      <c r="N87" s="39" t="s">
         <v>60</v>
       </c>
       <c r="O87" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="P87" s="38" t="s">
+      <c r="P87" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="Q87" s="38"/>
-      <c r="R87" s="38" t="s">
+      <c r="Q87" s="39"/>
+      <c r="R87" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="S87" s="38" t="s">
+      <c r="S87" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="T87" s="38" t="s">
+      <c r="T87" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="U87" s="38" t="s">
+      <c r="U87" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="V87" s="38" t="s">
+      <c r="V87" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="W87" s="38" t="s">
+      <c r="W87" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="X87" s="38" t="s">
+      <c r="X87" s="39" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="88" ht="15" spans="1:24">
-      <c r="A88" s="38"/>
-      <c r="B88" s="40">
-        <v>46305</v>
-      </c>
-      <c r="C88" s="41">
-        <v>900000</v>
-      </c>
-      <c r="D88" s="45">
+      <c r="A88" s="39"/>
+      <c r="B88" s="41">
+        <v>46663</v>
+      </c>
+      <c r="C88" s="42">
+        <v>9000000</v>
+      </c>
+      <c r="D88" s="46">
         <f>F88-E84+1</f>
-        <v>421</v>
+        <v>377</v>
       </c>
       <c r="E88" s="16">
         <v>46204</v>
       </c>
-      <c r="F88" s="42">
+      <c r="F88" s="43">
         <v>46664</v>
       </c>
-      <c r="G88" s="35">
+      <c r="G88" s="36">
+        <f t="shared" ref="G88:G92" si="24">G86</f>
+        <v>70</v>
+      </c>
+      <c r="H88" s="44">
         <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="H88" s="43">
-        <f t="shared" si="20"/>
-        <v>0.015</v>
-      </c>
-      <c r="I88" s="53">
+        <v>0.02</v>
+      </c>
+      <c r="I88" s="54">
         <f t="shared" si="16"/>
-        <v>15571.2328767123</v>
-      </c>
-      <c r="J88" s="54">
+        <v>185917.808219178</v>
+      </c>
+      <c r="J88" s="55">
         <f t="shared" si="17"/>
-        <v>15571.2328767123</v>
-      </c>
-      <c r="K88" s="37"/>
-      <c r="L88" s="40">
+        <v>185917.808219178</v>
+      </c>
+      <c r="K88" s="38"/>
+      <c r="L88" s="41">
         <f t="shared" ref="L88:R88" si="25">B88</f>
-        <v>46305</v>
-      </c>
-      <c r="M88" s="41">
+        <v>46663</v>
+      </c>
+      <c r="M88" s="42">
         <f t="shared" si="25"/>
-        <v>900000</v>
-      </c>
-      <c r="N88" s="45">
+        <v>9000000</v>
+      </c>
+      <c r="N88" s="46">
         <f>P88-O84+1</f>
-        <v>421</v>
-      </c>
-      <c r="O88" s="47">
+        <v>377</v>
+      </c>
+      <c r="O88" s="48">
         <f t="shared" si="25"/>
         <v>46204</v>
       </c>
-      <c r="P88" s="42">
+      <c r="P88" s="43">
         <f t="shared" si="25"/>
         <v>46664</v>
       </c>
-      <c r="Q88" s="35">
+      <c r="Q88" s="36">
         <f t="shared" si="25"/>
-        <v>80</v>
-      </c>
-      <c r="R88" s="43">
+        <v>70</v>
+      </c>
+      <c r="R88" s="44">
         <f t="shared" si="25"/>
-        <v>0.015</v>
-      </c>
-      <c r="S88" s="48">
+        <v>0.02</v>
+      </c>
+      <c r="S88" s="49">
+        <f t="shared" si="21"/>
+        <v>206465.753424658</v>
+      </c>
+      <c r="T88" s="55">
+        <f>S88+W86</f>
+        <v>260164.383561644</v>
+      </c>
+      <c r="U88" s="56">
+        <f>L88-O84</f>
+        <v>375</v>
+      </c>
+      <c r="V88" s="56">
         <f t="shared" si="22"/>
-        <v>15571.2328767123</v>
-      </c>
-      <c r="T88" s="54">
-        <f>S88+W86</f>
-        <v>16845.2054794521</v>
-      </c>
-      <c r="U88" s="55">
-        <f>L88-O84</f>
-        <v>61</v>
-      </c>
-      <c r="V88" s="55">
+        <v>2</v>
+      </c>
+      <c r="W88" s="53">
+        <f>M86*R88*U88/365</f>
+        <v>205479.452054795</v>
+      </c>
+      <c r="X88" s="53">
         <f t="shared" si="23"/>
-        <v>360</v>
-      </c>
-      <c r="W88" s="52">
-        <f>M86*R88*U88/365</f>
-        <v>2256.16438356164</v>
-      </c>
-      <c r="X88" s="52">
-        <f t="shared" si="24"/>
-        <v>13315.0684931507</v>
-      </c>
-    </row>
-    <row r="89" ht="57" spans="1:24">
-      <c r="A89" s="38" t="s">
+        <v>986.301369863014</v>
+      </c>
+    </row>
+    <row r="89" ht="42.75" spans="1:24">
+      <c r="A89" s="39" t="s">
         <v>71</v>
       </c>
-      <c r="B89" s="38" t="s">
+      <c r="B89" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="C89" s="38" t="s">
+      <c r="C89" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="D89" s="38" t="s">
+      <c r="D89" s="39" t="s">
         <v>60</v>
       </c>
       <c r="E89" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="F89" s="38" t="s">
+      <c r="F89" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="G89" s="38"/>
-      <c r="H89" s="38" t="s">
+      <c r="G89" s="39"/>
+      <c r="H89" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="I89" s="38" t="s">
+      <c r="I89" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="J89" s="38" t="s">
+      <c r="J89" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="K89" s="37"/>
-      <c r="L89" s="38" t="s">
+      <c r="K89" s="38"/>
+      <c r="L89" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="M89" s="38" t="s">
+      <c r="M89" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="N89" s="38" t="s">
+      <c r="N89" s="39" t="s">
         <v>60</v>
       </c>
       <c r="O89" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="P89" s="38" t="s">
+      <c r="P89" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="Q89" s="38"/>
-      <c r="R89" s="38" t="s">
+      <c r="Q89" s="39"/>
+      <c r="R89" s="39" t="s">
         <v>52</v>
       </c>
-      <c r="S89" s="38" t="s">
+      <c r="S89" s="39" t="s">
         <v>79</v>
       </c>
-      <c r="T89" s="38" t="s">
+      <c r="T89" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="U89" s="38" t="s">
+      <c r="U89" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="V89" s="38" t="s">
+      <c r="V89" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="W89" s="38" t="s">
+      <c r="W89" s="39" t="s">
         <v>67</v>
       </c>
-      <c r="X89" s="38" t="s">
+      <c r="X89" s="39" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="90" ht="15" spans="1:24">
-      <c r="A90" s="38"/>
-      <c r="B90" s="40">
-        <v>46366</v>
-      </c>
-      <c r="C90" s="41">
-        <v>500000</v>
-      </c>
-      <c r="D90" s="35">
+      <c r="A90" s="39"/>
+      <c r="B90" s="41">
+        <v>46690</v>
+      </c>
+      <c r="C90" s="42">
+        <v>5000000</v>
+      </c>
+      <c r="D90" s="36">
         <f>F90-E84+1</f>
-        <v>421</v>
+        <v>434</v>
       </c>
       <c r="E90" s="16">
         <v>46204</v>
       </c>
-      <c r="F90" s="42">
-        <v>46664</v>
-      </c>
-      <c r="G90" s="35">
+      <c r="F90" s="43">
+        <v>46721</v>
+      </c>
+      <c r="G90" s="36">
+        <f t="shared" si="24"/>
+        <v>70</v>
+      </c>
+      <c r="H90" s="44">
         <f t="shared" si="19"/>
-        <v>80</v>
-      </c>
-      <c r="H90" s="43">
-        <f t="shared" si="20"/>
-        <v>0.015</v>
-      </c>
-      <c r="I90" s="56">
+        <v>0.02</v>
+      </c>
+      <c r="I90" s="57">
         <f>C90*D90*H90/365</f>
-        <v>8650.68493150685</v>
-      </c>
-      <c r="J90" s="46">
+        <v>118904.109589041</v>
+      </c>
+      <c r="J90" s="47">
         <f>I90</f>
-        <v>8650.68493150685</v>
-      </c>
-      <c r="K90" s="37"/>
-      <c r="L90" s="40">
-        <f t="shared" ref="L90:R90" si="26">B90</f>
-        <v>46366</v>
-      </c>
-      <c r="M90" s="41">
-        <f t="shared" si="26"/>
-        <v>500000</v>
-      </c>
-      <c r="N90" s="35">
+        <v>118904.109589041</v>
+      </c>
+      <c r="K90" s="38"/>
+      <c r="L90" s="41">
+        <f>B90</f>
+        <v>46690</v>
+      </c>
+      <c r="M90" s="42">
+        <f t="shared" ref="L90:R90" si="26">C90</f>
+        <v>5000000</v>
+      </c>
+      <c r="N90" s="36">
         <f>P90-O84+1</f>
-        <v>421</v>
-      </c>
-      <c r="O90" s="47">
+        <v>434</v>
+      </c>
+      <c r="O90" s="48">
         <f t="shared" si="26"/>
         <v>46204</v>
       </c>
-      <c r="P90" s="42">
+      <c r="P90" s="43">
         <f t="shared" si="26"/>
-        <v>46664</v>
-      </c>
-      <c r="Q90" s="35">
+        <v>46721</v>
+      </c>
+      <c r="Q90" s="36">
         <f t="shared" si="26"/>
-        <v>80</v>
-      </c>
-      <c r="R90" s="43">
+        <v>70</v>
+      </c>
+      <c r="R90" s="44">
         <f t="shared" si="26"/>
-        <v>0.015</v>
-      </c>
-      <c r="S90" s="57">
+        <v>0.02</v>
+      </c>
+      <c r="S90" s="58">
+        <f t="shared" si="21"/>
+        <v>207013.698630137</v>
+      </c>
+      <c r="T90" s="50">
+        <f>S90+W88+W86</f>
+        <v>466191.780821918</v>
+      </c>
+      <c r="U90" s="51">
+        <f>L90-O84</f>
+        <v>402</v>
+      </c>
+      <c r="V90" s="51">
         <f t="shared" si="22"/>
-        <v>10656.1643835616</v>
-      </c>
-      <c r="T90" s="49">
-        <f>S90+W88+W86</f>
-        <v>14186.301369863</v>
-      </c>
-      <c r="U90" s="50">
-        <f>L90-O84</f>
-        <v>122</v>
-      </c>
-      <c r="V90" s="50">
+        <v>32</v>
+      </c>
+      <c r="W90" s="58">
+        <f>M88*U90*R90/365</f>
+        <v>198246.575342466</v>
+      </c>
+      <c r="X90" s="58">
         <f t="shared" si="23"/>
-        <v>299</v>
-      </c>
-      <c r="W90" s="57">
-        <f>M88*U90*R90/365</f>
-        <v>4512.32876712329</v>
-      </c>
-      <c r="X90" s="57">
+        <v>8767.12328767123</v>
+      </c>
+    </row>
+    <row r="91" ht="42.75" spans="1:24">
+      <c r="A91" s="39" t="s">
+        <v>86</v>
+      </c>
+      <c r="B91" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="C91" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D91" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="E91" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F91" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="G91" s="39"/>
+      <c r="H91" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="I91" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="J91" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="K91" s="38"/>
+      <c r="L91" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="M91" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="N91" s="39" t="s">
+        <v>60</v>
+      </c>
+      <c r="O91" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="P91" s="39" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q91" s="39"/>
+      <c r="R91" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="S91" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="T91" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="U91" s="39" t="s">
+        <v>65</v>
+      </c>
+      <c r="V91" s="39" t="s">
+        <v>66</v>
+      </c>
+      <c r="W91" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="X91" s="39" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="92" ht="15" spans="1:24">
+      <c r="A92" s="39"/>
+      <c r="B92" s="41">
+        <v>46691</v>
+      </c>
+      <c r="C92" s="42">
+        <v>4000000</v>
+      </c>
+      <c r="D92" s="36">
+        <f>F92-E84+1</f>
+        <v>434</v>
+      </c>
+      <c r="E92" s="16">
+        <v>46204</v>
+      </c>
+      <c r="F92" s="43">
+        <v>46721</v>
+      </c>
+      <c r="G92" s="36">
         <f t="shared" si="24"/>
-        <v>6143.83561643836</v>
+        <v>70</v>
+      </c>
+      <c r="H92" s="44">
+        <f>H90</f>
+        <v>0.02</v>
+      </c>
+      <c r="I92" s="57">
+        <f>C92*D92*H92/365</f>
+        <v>95123.2876712329</v>
+      </c>
+      <c r="J92" s="47">
+        <f>I92</f>
+        <v>95123.2876712329</v>
+      </c>
+      <c r="K92" s="38"/>
+      <c r="L92" s="41">
+        <f t="shared" ref="L92:R92" si="27">B92</f>
+        <v>46691</v>
+      </c>
+      <c r="M92" s="42">
+        <f t="shared" si="27"/>
+        <v>4000000</v>
+      </c>
+      <c r="N92" s="36">
+        <f>P92-O84+1</f>
+        <v>434</v>
+      </c>
+      <c r="O92" s="48">
+        <f t="shared" si="27"/>
+        <v>46204</v>
+      </c>
+      <c r="P92" s="43">
+        <f t="shared" si="27"/>
+        <v>46721</v>
+      </c>
+      <c r="Q92" s="36">
+        <f t="shared" si="27"/>
+        <v>70</v>
+      </c>
+      <c r="R92" s="44">
+        <f t="shared" si="27"/>
+        <v>0.02</v>
+      </c>
+      <c r="S92" s="58">
+        <f>W92+X92</f>
+        <v>117205.479452055</v>
+      </c>
+      <c r="T92" s="50">
+        <f>S92+W90+W88+W86</f>
+        <v>574630.136986301</v>
+      </c>
+      <c r="U92" s="51">
+        <f>L92-O84</f>
+        <v>403</v>
+      </c>
+      <c r="V92" s="51">
+        <f>N92-U92</f>
+        <v>31</v>
+      </c>
+      <c r="W92" s="58">
+        <f>M90*U92*R92/365</f>
+        <v>110410.95890411</v>
+      </c>
+      <c r="X92" s="58">
+        <f>M92*R92*V92/365</f>
+        <v>6794.52054794521</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="33">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="L1:U1"/>
     <mergeCell ref="F2:H2"/>
@@ -9886,6 +10100,7 @@
     <mergeCell ref="A85:A86"/>
     <mergeCell ref="A87:A88"/>
     <mergeCell ref="A89:A90"/>
+    <mergeCell ref="A91:A92"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
